--- a/ingestion/coa_track/letta-imb-coas/exports/Tranche_Two.xlsx
+++ b/ingestion/coa_track/letta-imb-coas/exports/Tranche_Two.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spec matrix" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iCoA issuance list" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificate index" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CoQ issuance plan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iCoA issuance list" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificate index" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Spec matrix'!$2:$4,'Spec matrix'!$A:$F</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'iCoA issuance list'!$A$2:$I$40</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'iCoA issuance list'!$2:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Certificate index'!$A$1:$H$108</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Certificate index'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CoQ issuance plan'!$A$2:$K$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'CoQ issuance plan'!$2:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'iCoA issuance list'!$A$2:$I$40</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'iCoA issuance list'!$2:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Certificate index'!$A$1:$H$108</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Certificate index'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -217,18 +220,18 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -253,18 +256,18 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1504,7 +1507,7 @@
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>•  Column C proposes the CoQ document code per QCSOP 012 v.03 §6.4.2 (CoQ-PP-[YYYY]-[NNNN], sequential per calendar year). Final numbers are assigned from the Certificate Issuance Register (QCLB 020) at approval — if any 2026 CoQ numbers are already consumed there, the sequence starts after the last used one.</t>
+          <t>•  Column C proposes the CoQ document code of each TESTING ROUND — one CoQ issuance event per sub-row, per QCSOP 012 v.03 §6.4.2 (CoQ-PP-[YYYY]-[NNNN], one sequential series per calendar year). The initial round's CoQ issues on completion of the initial QC sampling; a resampling (R) round produces a superseding CoQ with a new issue date that carries the resampled parameters' new results and reuses the non-resampled results from the earlier sampling's eCoAs (time-invariant parameters such as heavy metals and pesticides). Codes run in results-complete chronology — see the 'CoQ issuance plan' sheet for each event's basis date, resampled vs carried-forward parameters and supersession chain. Final numbers are assigned from the Certificate Issuance Register (QCLB 020) at approval — if any 2026 CoQ numbers are already consumed there, the sequence starts after the last used one.</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2807,7 @@
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0003</t>
+          <t>CoQ-PP-2026-0015</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -2812,27 +2815,27 @@
           <t>GP0824_03</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>P050072</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>GP_THC24:CBD1</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>R1 · Jun–Jul 2025</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -2842,7 +2845,7 @@
           <t>iCoA-PP-2026-0006 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K5" s="23" t="inlineStr">
+      <c r="K5" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -2865,7 +2868,7 @@
       <c r="O5" s="27" t="n">
         <v>25.45</v>
       </c>
-      <c r="P5" s="23" t="inlineStr">
+      <c r="P5" s="19" t="inlineStr">
         <is>
           <t>Grade II, 22.00 – 26.00</t>
         </is>
@@ -2893,7 +2896,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V5" s="23" t="inlineStr">
+      <c r="V5" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -2911,7 +2914,7 @@
           <t>ППК25175, 10.07.2025, CNP</t>
         </is>
       </c>
-      <c r="Z5" s="23" t="inlineStr">
+      <c r="Z5" s="19" t="inlineStr">
         <is>
           <t>1.1×10⁴</t>
         </is>
@@ -2921,7 +2924,7 @@
           <t>628/1129/25, 02.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AB5" s="23" t="inlineStr">
+      <c r="AB5" s="19" t="inlineStr">
         <is>
           <t>1.2×10³</t>
         </is>
@@ -2931,7 +2934,7 @@
           <t>628/1129/25, 02.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AD5" s="23" t="inlineStr">
+      <c r="AD5" s="19" t="inlineStr">
         <is>
           <t>&lt;10¹ and &gt;10³</t>
         </is>
@@ -2941,7 +2944,7 @@
           <t>628/1129/25, 02.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AF5" s="23" t="inlineStr">
+      <c r="AF5" s="19" t="inlineStr">
         <is>
           <t>Одговара (absent)</t>
         </is>
@@ -2951,7 +2954,7 @@
           <t>628/1129/25, 02.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AH5" s="23" t="inlineStr">
+      <c r="AH5" s="19" t="inlineStr">
         <is>
           <t>Одговара (absent)</t>
         </is>
@@ -2971,7 +2974,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL5" s="23" t="inlineStr">
+      <c r="AL5" s="19" t="inlineStr">
         <is>
           <t>&lt;2</t>
         </is>
@@ -2991,7 +2994,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AP5" s="23" t="inlineStr">
+      <c r="AP5" s="19" t="inlineStr">
         <is>
           <t>N.D.</t>
         </is>
@@ -3001,7 +3004,7 @@
           <t>3178/2025, 26.06.2025, IPH</t>
         </is>
       </c>
-      <c r="AR5" s="23" t="inlineStr">
+      <c r="AR5" s="19" t="inlineStr">
         <is>
           <t>N.D.</t>
         </is>
@@ -3019,7 +3022,7 @@
           <t>3178/2025, 26.06.2025, IPH</t>
         </is>
       </c>
-      <c r="AV5" s="23" t="inlineStr">
+      <c r="AV5" s="19" t="inlineStr">
         <is>
           <t>N.D.</t>
         </is>
@@ -3029,7 +3032,7 @@
           <t>3178/2025, 26.06.2025, IPH</t>
         </is>
       </c>
-      <c r="AX5" s="23" t="inlineStr">
+      <c r="AX5" s="19" t="inlineStr">
         <is>
           <t>ND / &lt;LOQ (13 analytes)</t>
         </is>
@@ -3051,7 +3054,7 @@
       </c>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0005</t>
+          <t>CoQ-PP-2026-0017</t>
         </is>
       </c>
       <c r="D6" s="32" t="inlineStr">
@@ -3059,27 +3062,27 @@
           <t>MB0824_05</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>P050112</t>
         </is>
       </c>
-      <c r="F6" s="33" t="inlineStr">
+      <c r="F6" s="34" t="inlineStr">
         <is>
           <t>Motor Breath</t>
         </is>
       </c>
-      <c r="G6" s="33" t="inlineStr">
+      <c r="G6" s="34" t="inlineStr">
         <is>
           <t>MB_THC17.5:CBD1</t>
         </is>
       </c>
-      <c r="H6" s="34" t="inlineStr">
+      <c r="H6" s="35" t="inlineStr">
         <is>
           <t>R1 · Jul 2025</t>
         </is>
       </c>
-      <c r="I6" s="35" t="inlineStr">
+      <c r="I6" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -3089,7 +3092,7 @@
           <t>iCoA-PP-2026-0010 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K6" s="35" t="inlineStr">
+      <c r="K6" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -3112,7 +3115,7 @@
       <c r="O6" s="39" t="n">
         <v>16.82</v>
       </c>
-      <c r="P6" s="35" t="inlineStr">
+      <c r="P6" s="31" t="inlineStr">
         <is>
           <t>Grade III, 15.00 – 20.00</t>
         </is>
@@ -3140,7 +3143,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V6" s="35" t="inlineStr">
+      <c r="V6" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -3158,7 +3161,7 @@
           <t>ППК52211, 28.07.2025, CNP</t>
         </is>
       </c>
-      <c r="Z6" s="35" t="inlineStr">
+      <c r="Z6" s="31" t="inlineStr">
         <is>
           <t>3.5×10³</t>
         </is>
@@ -3168,7 +3171,7 @@
           <t>767/1376/25, 29.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AB6" s="35" t="inlineStr">
+      <c r="AB6" s="31" t="inlineStr">
         <is>
           <t>1×10³</t>
         </is>
@@ -3178,7 +3181,7 @@
           <t>767/1376/25, 29.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AD6" s="35" t="inlineStr">
+      <c r="AD6" s="31" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -3188,7 +3191,7 @@
           <t>767/1376/25, 29.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AF6" s="35" t="inlineStr">
+      <c r="AF6" s="31" t="inlineStr">
         <is>
           <t>Одговара (absent)</t>
         </is>
@@ -3198,7 +3201,7 @@
           <t>767/1376/25, 29.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AH6" s="35" t="inlineStr">
+      <c r="AH6" s="31" t="inlineStr">
         <is>
           <t>Одговара (absent)</t>
         </is>
@@ -3236,7 +3239,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AP6" s="35" t="inlineStr">
+      <c r="AP6" s="31" t="inlineStr">
         <is>
           <t>N.D.</t>
         </is>
@@ -3246,7 +3249,7 @@
           <t>3638/2025, 28.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AR6" s="35" t="inlineStr">
+      <c r="AR6" s="31" t="inlineStr">
         <is>
           <t>N.D.</t>
         </is>
@@ -3272,7 +3275,7 @@
           <t>3638/2025, 28.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AX6" s="35" t="inlineStr">
+      <c r="AX6" s="31" t="inlineStr">
         <is>
           <t>ND / &lt;LOQ (13 analytes)</t>
         </is>
@@ -3294,7 +3297,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0010</t>
+          <t>CoQ-PP-2026-0007</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -3302,27 +3305,27 @@
           <t>GG1024</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>Gorilla Glue</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>GG_THC15:CBD1</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>R1 · Apr 2025</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -3332,7 +3335,7 @@
           <t>n/a — Purely Plant in-house CoA (Batch GG1024, no certificate/report number printed), 23.04.2025, PP</t>
         </is>
       </c>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="K7" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -3342,7 +3345,7 @@
           <t>iCoA-PP-2026-0019 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="M7" s="23" t="inlineStr">
+      <c r="M7" s="19" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -3355,7 +3358,7 @@
       <c r="O7" s="27" t="n">
         <v>13.34</v>
       </c>
-      <c r="P7" s="23" t="inlineStr">
+      <c r="P7" s="19" t="inlineStr">
         <is>
           <t>Grade III, 12.34 – 18.00</t>
         </is>
@@ -3383,7 +3386,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V7" s="23" t="inlineStr">
+      <c r="V7" s="19" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -3403,7 +3406,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z7" s="23" t="inlineStr">
+      <c r="Z7" s="19" t="inlineStr">
         <is>
           <t>1.1·10^4</t>
         </is>
@@ -3413,7 +3416,7 @@
           <t>n/a — Purely Plant in-house CoA (Batch GG1024, no certificate/report number printed), 23.04.2025, CNP</t>
         </is>
       </c>
-      <c r="AB7" s="23" t="inlineStr">
+      <c r="AB7" s="19" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -3423,7 +3426,7 @@
           <t>n/a — Purely Plant in-house CoA (Batch GG1024, no certificate/report number printed), 23.04.2025, CNP</t>
         </is>
       </c>
-      <c r="AD7" s="23" t="inlineStr">
+      <c r="AD7" s="19" t="inlineStr">
         <is>
           <t>&lt;10^2 &gt;10</t>
         </is>
@@ -3433,7 +3436,7 @@
           <t>n/a — Purely Plant in-house CoA (Batch GG1024, no certificate/report number printed), 23.04.2025, CNP</t>
         </is>
       </c>
-      <c r="AF7" s="23" t="inlineStr">
+      <c r="AF7" s="19" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -3443,7 +3446,7 @@
           <t>n/a — Purely Plant in-house CoA (Batch GG1024, no certificate/report number printed), 23.04.2025, CNP</t>
         </is>
       </c>
-      <c r="AH7" s="23" t="inlineStr">
+      <c r="AH7" s="19" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -3463,7 +3466,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL7" s="23" t="inlineStr">
+      <c r="AL7" s="19" t="inlineStr">
         <is>
           <t>&lt;2</t>
         </is>
@@ -3515,7 +3518,7 @@
           <t>n/a — Purely Plant in-house CoA (Batch GG1024, no certificate/report number printed), 23.04.2025, CNP</t>
         </is>
       </c>
-      <c r="AX7" s="23" t="inlineStr">
+      <c r="AX7" s="19" t="inlineStr">
         <is>
           <t>ND / &lt;LOQ (13 analytes)</t>
         </is>
@@ -3537,7 +3540,7 @@
       </c>
       <c r="C8" s="31" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0016</t>
+          <t>CoQ-PP-2026-0010</t>
         </is>
       </c>
       <c r="D8" s="32" t="inlineStr">
@@ -3545,27 +3548,27 @@
           <t>OPM1024_01</t>
         </is>
       </c>
-      <c r="E8" s="31" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>P050042</t>
         </is>
       </c>
-      <c r="F8" s="33" t="inlineStr">
+      <c r="F8" s="34" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="G8" s="33" t="inlineStr">
+      <c r="G8" s="34" t="inlineStr">
         <is>
           <t>OPM_THC16:CBD1</t>
         </is>
       </c>
-      <c r="H8" s="34" t="inlineStr">
+      <c r="H8" s="35" t="inlineStr">
         <is>
           <t>R1 · May 2025</t>
         </is>
       </c>
-      <c r="I8" s="35" t="inlineStr">
+      <c r="I8" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -3575,7 +3578,7 @@
           <t>iCoA-PP-2026-0029 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K8" s="35" t="inlineStr">
+      <c r="K8" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -3598,7 +3601,7 @@
       <c r="O8" s="39" t="n">
         <v>15.38</v>
       </c>
-      <c r="P8" s="35" t="inlineStr">
+      <c r="P8" s="31" t="inlineStr">
         <is>
           <t>Grade III, 13.00 – 19.00</t>
         </is>
@@ -3626,7 +3629,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V8" s="35" t="inlineStr">
+      <c r="V8" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -3644,7 +3647,7 @@
           <t>ППК25117, 06.05.2025, CNP</t>
         </is>
       </c>
-      <c r="Z8" s="35" t="inlineStr">
+      <c r="Z8" s="31" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -3654,7 +3657,7 @@
           <t>407/0745/25, 07.05.2025, IPH</t>
         </is>
       </c>
-      <c r="AB8" s="35" t="inlineStr">
+      <c r="AB8" s="31" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -3664,7 +3667,7 @@
           <t>407/0745/25, 07.05.2025, IPH</t>
         </is>
       </c>
-      <c r="AD8" s="35" t="inlineStr">
+      <c r="AD8" s="31" t="inlineStr">
         <is>
           <t>&lt;10² and &gt;10</t>
         </is>
@@ -3674,7 +3677,7 @@
           <t>407/0745/25, 07.05.2025, IPH</t>
         </is>
       </c>
-      <c r="AF8" s="35" t="inlineStr">
+      <c r="AF8" s="31" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -3684,7 +3687,7 @@
           <t>407/0745/25, 07.05.2025, IPH</t>
         </is>
       </c>
-      <c r="AH8" s="35" t="inlineStr">
+      <c r="AH8" s="31" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -3704,7 +3707,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL8" s="35" t="inlineStr">
+      <c r="AL8" s="31" t="inlineStr">
         <is>
           <t>&lt;2</t>
         </is>
@@ -3756,7 +3759,7 @@
           <t>2156/2025, 07.05.2025, IPH</t>
         </is>
       </c>
-      <c r="AX8" s="35" t="inlineStr">
+      <c r="AX8" s="31" t="inlineStr">
         <is>
           <t>ND / &lt;LOQ (13 analytes)</t>
         </is>
@@ -3786,27 +3789,27 @@
           <t>OPM1024_03</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>P050082</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>OPM_THC16:CBD1</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t>R1 · Jul 2025</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -3816,7 +3819,7 @@
           <t>iCoA-PP-2026-0033 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K9" s="23" t="inlineStr">
+      <c r="K9" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -3839,7 +3842,7 @@
       <c r="O9" s="27" t="n">
         <v>16.55</v>
       </c>
-      <c r="P9" s="23" t="inlineStr">
+      <c r="P9" s="19" t="inlineStr">
         <is>
           <t>Grade III, 13.00 – 19.00</t>
         </is>
@@ -3867,7 +3870,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V9" s="23" t="inlineStr">
+      <c r="V9" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -3885,7 +3888,7 @@
           <t>ППК25210, 28.07.2025, CNP</t>
         </is>
       </c>
-      <c r="Z9" s="23" t="inlineStr">
+      <c r="Z9" s="19" t="inlineStr">
         <is>
           <t>2×10²</t>
         </is>
@@ -3895,7 +3898,7 @@
           <t>766/1375/25, 29.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AB9" s="23" t="inlineStr">
+      <c r="AB9" s="19" t="inlineStr">
         <is>
           <t>3×10²</t>
         </is>
@@ -3905,7 +3908,7 @@
           <t>766/1375/25, 29.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AD9" s="23" t="inlineStr">
+      <c r="AD9" s="19" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -3915,7 +3918,7 @@
           <t>766/1375/25, 29.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AF9" s="23" t="inlineStr">
+      <c r="AF9" s="19" t="inlineStr">
         <is>
           <t>Одговара (absent)</t>
         </is>
@@ -3925,7 +3928,7 @@
           <t>766/1375/25, 29.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AH9" s="23" t="inlineStr">
+      <c r="AH9" s="19" t="inlineStr">
         <is>
           <t>Одговара (absent)</t>
         </is>
@@ -3963,7 +3966,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AP9" s="23" t="inlineStr">
+      <c r="AP9" s="19" t="inlineStr">
         <is>
           <t>N.D.</t>
         </is>
@@ -3973,7 +3976,7 @@
           <t>3636/2025, 28.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AR9" s="23" t="inlineStr">
+      <c r="AR9" s="19" t="inlineStr">
         <is>
           <t>N.D.</t>
         </is>
@@ -3999,7 +4002,7 @@
           <t>3636/2025, 28.07.2025, IPH</t>
         </is>
       </c>
-      <c r="AX9" s="23" t="inlineStr">
+      <c r="AX9" s="19" t="inlineStr">
         <is>
           <t>ND / &lt;LOQ (13 analytes)</t>
         </is>
@@ -4021,7 +4024,7 @@
       </c>
       <c r="C10" s="31" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0019</t>
+          <t>CoQ-PP-2026-0029</t>
         </is>
       </c>
       <c r="D10" s="32" t="inlineStr">
@@ -4029,27 +4032,27 @@
           <t>BSS052501</t>
         </is>
       </c>
-      <c r="E10" s="31" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>P050192</t>
         </is>
       </c>
-      <c r="F10" s="33" t="inlineStr">
+      <c r="F10" s="34" t="inlineStr">
         <is>
           <t>Blue Sunset Sherbet</t>
         </is>
       </c>
-      <c r="G10" s="33" t="inlineStr">
+      <c r="G10" s="34" t="inlineStr">
         <is>
           <t>BSS_THC22:CBD1</t>
         </is>
       </c>
-      <c r="H10" s="34" t="inlineStr">
+      <c r="H10" s="35" t="inlineStr">
         <is>
           <t>R1 · Nov–Dec 2025</t>
         </is>
       </c>
-      <c r="I10" s="35" t="inlineStr">
+      <c r="I10" s="31" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -4059,7 +4062,7 @@
           <t>PP CoA #017, 04.12.2025, PP</t>
         </is>
       </c>
-      <c r="K10" s="35" t="inlineStr">
+      <c r="K10" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -4069,7 +4072,7 @@
           <t>iCoA-PP-2026-0034 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="M10" s="35" t="inlineStr">
+      <c r="M10" s="31" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -4082,7 +4085,7 @@
       <c r="O10" s="39" t="n">
         <v>20.39</v>
       </c>
-      <c r="P10" s="35" t="inlineStr">
+      <c r="P10" s="31" t="inlineStr">
         <is>
           <t>Grade II, 19.39 – 24.75</t>
         </is>
@@ -4110,7 +4113,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V10" s="35" t="inlineStr">
+      <c r="V10" s="31" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -4144,7 +4147,7 @@
           <t>1157/2058/25, 24.11.2025, IPH</t>
         </is>
       </c>
-      <c r="AD10" s="35" t="inlineStr">
+      <c r="AD10" s="31" t="inlineStr">
         <is>
           <t>&lt; 10^2 and &gt; 10</t>
         </is>
@@ -4154,7 +4157,7 @@
           <t>1157/2058/25, 24.11.2025, IPH</t>
         </is>
       </c>
-      <c r="AF10" s="35" t="inlineStr">
+      <c r="AF10" s="31" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -4164,7 +4167,7 @@
           <t>1157/2058/25, 24.11.2025, IPH</t>
         </is>
       </c>
-      <c r="AH10" s="35" t="inlineStr">
+      <c r="AH10" s="31" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -4174,7 +4177,7 @@
           <t>1157/2058/25, 24.11.2025, IPH</t>
         </is>
       </c>
-      <c r="AJ10" s="35" t="inlineStr">
+      <c r="AJ10" s="31" t="inlineStr">
         <is>
           <t>ND</t>
         </is>
@@ -4194,7 +4197,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AN10" s="35" t="inlineStr">
+      <c r="AN10" s="31" t="inlineStr">
         <is>
           <t>&lt;LOQ</t>
         </is>
@@ -4236,7 +4239,7 @@
           <t>5661/2025, 01.12.2025, IPH</t>
         </is>
       </c>
-      <c r="AX10" s="35" t="inlineStr">
+      <c r="AX10" s="31" t="inlineStr">
         <is>
           <t>Pesticide residue screen (471 residues: 265 LC/MS/MS Annex 1 + 206 GC/MS/MS Annex 2, MKC EN 15662:2011): Not found any pesticide above LOQ (≤LOQ) — COMPLIES with USP and Ph.Eur.</t>
         </is>
@@ -4266,27 +4269,27 @@
           <t>HPA052501</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>P050182</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>High Pro Amnesia</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>HPA_THC22:CBD1</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t>R1 · Sep 2025</t>
         </is>
       </c>
-      <c r="I11" s="23" t="inlineStr">
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -4296,7 +4299,7 @@
           <t>iCoA-PP-2026-0042 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K11" s="23" t="inlineStr">
+      <c r="K11" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -4319,7 +4322,7 @@
       <c r="O11" s="27" t="n">
         <v>20.39</v>
       </c>
-      <c r="P11" s="23" t="inlineStr">
+      <c r="P11" s="19" t="inlineStr">
         <is>
           <t>Grade II, 19.39 – 24.75</t>
         </is>
@@ -4347,7 +4350,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V11" s="23" t="inlineStr">
+      <c r="V11" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -4365,7 +4368,7 @@
           <t>ППК25278, 19.09.2025, CNP</t>
         </is>
       </c>
-      <c r="Z11" s="23" t="inlineStr">
+      <c r="Z11" s="19" t="inlineStr">
         <is>
           <t>2.7×10⁴</t>
         </is>
@@ -4375,7 +4378,7 @@
           <t>948/1686/25, 17.09.2025, IPH</t>
         </is>
       </c>
-      <c r="AB11" s="23" t="inlineStr">
+      <c r="AB11" s="19" t="inlineStr">
         <is>
           <t>2.6×10⁴</t>
         </is>
@@ -4385,7 +4388,7 @@
           <t>948/1686/25, 17.09.2025, IPH</t>
         </is>
       </c>
-      <c r="AD11" s="23" t="inlineStr">
+      <c r="AD11" s="19" t="inlineStr">
         <is>
           <t>&lt;10¹</t>
         </is>
@@ -4395,7 +4398,7 @@
           <t>948/1686/25, 17.09.2025, IPH</t>
         </is>
       </c>
-      <c r="AF11" s="23" t="inlineStr">
+      <c r="AF11" s="19" t="inlineStr">
         <is>
           <t>Одговара (absent)</t>
         </is>
@@ -4405,7 +4408,7 @@
           <t>948/1686/25, 17.09.2025, IPH</t>
         </is>
       </c>
-      <c r="AH11" s="23" t="inlineStr">
+      <c r="AH11" s="19" t="inlineStr">
         <is>
           <t>Одговара (absent)</t>
         </is>
@@ -4425,7 +4428,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL11" s="23" t="inlineStr">
+      <c r="AL11" s="19" t="inlineStr">
         <is>
           <t>&lt;2</t>
         </is>
@@ -4453,7 +4456,7 @@
           <t>4352/2025, 15.09.2025, IPH</t>
         </is>
       </c>
-      <c r="AR11" s="23" t="inlineStr">
+      <c r="AR11" s="19" t="inlineStr">
         <is>
           <t>N.D.</t>
         </is>
@@ -4463,7 +4466,7 @@
           <t>4352/2025, 15.09.2025, IPH</t>
         </is>
       </c>
-      <c r="AT11" s="23" t="inlineStr">
+      <c r="AT11" s="19" t="inlineStr">
         <is>
           <t>N.D.</t>
         </is>
@@ -4473,7 +4476,7 @@
           <t>4352/2025, 15.09.2025, IPH</t>
         </is>
       </c>
-      <c r="AV11" s="23" t="inlineStr">
+      <c r="AV11" s="19" t="inlineStr">
         <is>
           <t>N.D.</t>
         </is>
@@ -4483,7 +4486,7 @@
           <t>4352/2025, 15.09.2025, IPH</t>
         </is>
       </c>
-      <c r="AX11" s="23" t="inlineStr">
+      <c r="AX11" s="19" t="inlineStr">
         <is>
           <t>ND / &lt;LOQ (13 analytes)</t>
         </is>
@@ -4505,7 +4508,7 @@
       </c>
       <c r="C12" s="31" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0025</t>
+          <t>CoQ-PP-2026-0026</t>
         </is>
       </c>
       <c r="D12" s="32" t="inlineStr">
@@ -4513,27 +4516,27 @@
           <t>CJ062501/1</t>
         </is>
       </c>
-      <c r="E12" s="31" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>P050222</t>
         </is>
       </c>
-      <c r="F12" s="33" t="inlineStr">
+      <c r="F12" s="34" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
       </c>
-      <c r="G12" s="33" t="inlineStr">
+      <c r="G12" s="34" t="inlineStr">
         <is>
           <t>CJ_THC22.5:CBD1</t>
         </is>
       </c>
-      <c r="H12" s="34" t="inlineStr">
+      <c r="H12" s="35" t="inlineStr">
         <is>
           <t>R1 · Oct–Dec 2025</t>
         </is>
       </c>
-      <c r="I12" s="35" t="inlineStr">
+      <c r="I12" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -4543,7 +4546,7 @@
           <t>iCoA-PP-2026-0046 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K12" s="35" t="inlineStr">
+      <c r="K12" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -4553,7 +4556,7 @@
           <t>iCoA-PP-2026-0046 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="M12" s="35" t="inlineStr">
+      <c r="M12" s="31" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -4566,7 +4569,7 @@
       <c r="O12" s="39" t="n">
         <v>21.51</v>
       </c>
-      <c r="P12" s="35" t="inlineStr">
+      <c r="P12" s="31" t="inlineStr">
         <is>
           <t>Grade II, 19.75 – 25.25</t>
         </is>
@@ -4594,7 +4597,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V12" s="35" t="inlineStr">
+      <c r="V12" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -4612,7 +4615,7 @@
           <t>ППК25321, 23.10.2025, CNP</t>
         </is>
       </c>
-      <c r="Z12" s="35" t="inlineStr">
+      <c r="Z12" s="31" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -4630,7 +4633,7 @@
           <t>1217/2168/25, 01.12.2025, IPH</t>
         </is>
       </c>
-      <c r="AD12" s="35" t="inlineStr">
+      <c r="AD12" s="31" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -4640,7 +4643,7 @@
           <t>1217/2168/25, 01.12.2025, IPH</t>
         </is>
       </c>
-      <c r="AF12" s="35" t="inlineStr">
+      <c r="AF12" s="31" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -4650,7 +4653,7 @@
           <t>1217/2168/25, 01.12.2025, IPH</t>
         </is>
       </c>
-      <c r="AH12" s="35" t="inlineStr">
+      <c r="AH12" s="31" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -4670,7 +4673,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL12" s="35" t="inlineStr">
+      <c r="AL12" s="31" t="inlineStr">
         <is>
           <t>&lt;2</t>
         </is>
@@ -4722,7 +4725,7 @@
           <t>4907/2025, 24.10.2025, IPH</t>
         </is>
       </c>
-      <c r="AX12" s="35" t="inlineStr">
+      <c r="AX12" s="31" t="inlineStr">
         <is>
           <t>Lindan (Gama HCH): Н.д. (not detected); Aldrin: Н.д. (not detected); Dieldrin i Aldrin (expressed as Dieldrin): Н.д. (not detected); HCB (Hexachlorobenzene): Н.д. (not detected); 4,4' DDE: Н.д. (not detected); 4,4' DDD: Н.д. (not detected); 4,4' DDT: Н.д. (not detected); Vkupno DDT (Total DDT): Н.д. (not detected); delta HCH: Н.д. (not detected); alpha HCH: Н.д. (not detected); beta HCH: Н.д. (not detected); Endrin: Н.д. (not detected); Chlorpyriphos-methyl: Н.д. (not detected); Chlorpyrifos (Chlorpyriphos-ethyl): Н.д. (not detected); Heptachlor (sum of Heptachlor + Heptachlor epoxide): Н.д. (not detected); Endosulfan (alpha, beta and endosulfan sulfate): Н.д. (not detected); Deltamethrin: Н.д. (not detected); Chlordane (sum of cis- and trans-chlordane): Н.д. (not detected); Metoxychlor: Н.д. (not detected); Heptachlor epoxide: Н.д. (not detected); Endrin aldehyde: Н.д. (not detected); alpha Endosulfan: Н.д. (not detected); beta Endosulfan: Н.д. (not detected); Endrin keton: Н.д. (not detected); trans-Chlordane: Н.д. (not detected); cis-Chlordane: Н.д. (not detected); Dieldrin: Н.д. (not detected); Heptachlor: Н.д. (not detected); Endosulfan sulfate: Н.д. (not detected)</t>
         </is>
@@ -4744,7 +4747,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0029</t>
+          <t>CoQ-PP-2026-0030</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -4752,27 +4755,27 @@
           <t>CLE072501</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>P050282</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>Clemosa a bud</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>CLE_THC7.5:CBD1</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t>R1 · Nov 2025 – Jan 2026</t>
         </is>
       </c>
-      <c r="I13" s="23" t="inlineStr">
+      <c r="I13" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -4782,7 +4785,7 @@
           <t>iCoA-PP-2026-0052 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K13" s="23" t="inlineStr">
+      <c r="K13" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -4805,7 +4808,7 @@
       <c r="O13" s="27" t="n">
         <v>8.02</v>
       </c>
-      <c r="P13" s="23" t="inlineStr">
+      <c r="P13" s="19" t="inlineStr">
         <is>
           <t>Grade V, 5.00 – 10.00</t>
         </is>
@@ -4833,7 +4836,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V13" s="23" t="inlineStr">
+      <c r="V13" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -4851,7 +4854,7 @@
           <t>PP CoA #027 / ППК25370, 21.01.2026, CNP</t>
         </is>
       </c>
-      <c r="Z13" s="23" t="inlineStr">
+      <c r="Z13" s="19" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -4861,7 +4864,7 @@
           <t>1219/2170/25, 26.11.2025, IPH</t>
         </is>
       </c>
-      <c r="AB13" s="23" t="inlineStr">
+      <c r="AB13" s="19" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -4871,7 +4874,7 @@
           <t>1219/2170/25, 26.11.2025, IPH</t>
         </is>
       </c>
-      <c r="AD13" s="23" t="inlineStr">
+      <c r="AD13" s="19" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -4881,7 +4884,7 @@
           <t>1219/2170/25, 26.11.2025, IPH</t>
         </is>
       </c>
-      <c r="AF13" s="23" t="inlineStr">
+      <c r="AF13" s="19" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -4891,7 +4894,7 @@
           <t>1219/2170/25, 26.11.2025, IPH</t>
         </is>
       </c>
-      <c r="AH13" s="23" t="inlineStr">
+      <c r="AH13" s="19" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -4961,7 +4964,7 @@
           <t>5700/2025, 02.12.2025, IPH</t>
         </is>
       </c>
-      <c r="AX13" s="23" t="inlineStr">
+      <c r="AX13" s="19" t="inlineStr">
         <is>
           <t>Lindan (Gama HCH): Н.д. (not detected); Aldrin: Н.д. (not detected); Dieldrin i Aldrin (expressed as Dieldrin): Н.д. (not detected); HCB (Hexachlorobenzene): Н.д. (not detected); 4,4' DDE: Н.д. (not detected); 4,4' DDD: Н.д. (not detected); 4,4' DDT: Н.д. (not detected); Vkupno DDT (Total DDT): Н.д. (not detected); delta HCH: Н.д. (not detected); alpha HCH: Н.д. (not detected); beta HCH: Н.д. (not detected); Endrin: Н.д. (not detected); Chlorpyriphos-methyl: Н.д. (not detected); Chlorpyrifos (Chlorpyriphos-ethyl): Н.д. (not detected); Heptachlor (sum of Heptachlor + Heptachlor epoxide): Н.д. (not detected); Endosulfan (alpha, beta and endosulfan sulfate): Н.д. (not detected); Deltamethrin: Н.д. (not detected); Chlordane (sum of cis- and trans-chlordane): Н.д. (not detected); Metoxychlor: Н.д. (not detected); Heptachlor epoxide: Н.д. (not detected); Endrin aldehyde: Н.д. (not detected); alpha Endosulfan: Н.д. (not detected); beta Endosulfan: Н.д. (not detected); Endrin keton: Н.д. (not detected); trans-Chlordane: Н.д. (not detected); cis-Chlordane: Н.д. (not detected); Dieldrin: Н.д. (not detected); Heptachlor: Н.д. (not detected); Endosulfan sulfate: Н.д. (not detected)</t>
         </is>
@@ -4983,7 +4986,7 @@
       </c>
       <c r="C14" s="31" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0031</t>
+          <t>CoQ-PP-2026-0032</t>
         </is>
       </c>
       <c r="D14" s="32" t="inlineStr">
@@ -4991,27 +4994,27 @@
           <t>GP072501/2</t>
         </is>
       </c>
-      <c r="E14" s="31" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>P050302</t>
         </is>
       </c>
-      <c r="F14" s="33" t="inlineStr">
+      <c r="F14" s="34" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
       </c>
-      <c r="G14" s="33" t="inlineStr">
+      <c r="G14" s="34" t="inlineStr">
         <is>
           <t>GP_THC20:CBD1</t>
         </is>
       </c>
-      <c r="H14" s="34" t="inlineStr">
+      <c r="H14" s="35" t="inlineStr">
         <is>
           <t>R1 · Dec 2025 – Jan 2026</t>
         </is>
       </c>
-      <c r="I14" s="35" t="inlineStr">
+      <c r="I14" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -5021,7 +5024,7 @@
           <t>iCoA-PP-2026-0056 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K14" s="35" t="inlineStr">
+      <c r="K14" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -5044,7 +5047,7 @@
       <c r="O14" s="39" t="n">
         <v>19.81</v>
       </c>
-      <c r="P14" s="35" t="inlineStr">
+      <c r="P14" s="31" t="inlineStr">
         <is>
           <t>Grade III, 18.00 – 22.00</t>
         </is>
@@ -5072,7 +5075,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V14" s="35" t="inlineStr">
+      <c r="V14" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -5090,7 +5093,7 @@
           <t>PP CoA #019 / ППК25379, 21.01.2026, CNP</t>
         </is>
       </c>
-      <c r="Z14" s="35" t="inlineStr">
+      <c r="Z14" s="31" t="inlineStr">
         <is>
           <t>2×10^2</t>
         </is>
@@ -5100,7 +5103,7 @@
           <t>1229/2195/25, Issued ~Dec 2025, IPH</t>
         </is>
       </c>
-      <c r="AB14" s="35" t="inlineStr">
+      <c r="AB14" s="31" t="inlineStr">
         <is>
           <t>3×10^2</t>
         </is>
@@ -5110,7 +5113,7 @@
           <t>1229/2195/25, Issued ~Dec 2025, IPH</t>
         </is>
       </c>
-      <c r="AD14" s="35" t="inlineStr">
+      <c r="AD14" s="31" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -5120,7 +5123,7 @@
           <t>1229/2195/25, Issued ~Dec 2025, IPH</t>
         </is>
       </c>
-      <c r="AF14" s="35" t="inlineStr">
+      <c r="AF14" s="31" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -5130,7 +5133,7 @@
           <t>1229/2195/25, Issued ~Dec 2025, IPH</t>
         </is>
       </c>
-      <c r="AH14" s="35" t="inlineStr">
+      <c r="AH14" s="31" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -5150,7 +5153,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL14" s="35" t="inlineStr">
+      <c r="AL14" s="31" t="inlineStr">
         <is>
           <t>&lt;2</t>
         </is>
@@ -5202,7 +5205,7 @@
           <t>5887/2025, 12.12.2025, IPH</t>
         </is>
       </c>
-      <c r="AX14" s="35" t="inlineStr">
+      <c r="AX14" s="31" t="inlineStr">
         <is>
           <t>Lindan (Gama HCH): Н.д. (not detected); Aldrin: Н.д. (not detected); Dieldrin i Aldrin (expressed as Dieldrin): Н.д. (not detected); HCB (Hexachlorobenzene): Н.д. (not detected); 4,4' DDE: Н.д. (not detected); 4,4' DDD: Н.д. (not detected); 4,4' DDT: Н.д. (not detected); Vkupno DDT (Total DDT): Н.д. (not detected); delta HCH: Н.д. (not detected); alpha HCH: Н.д. (not detected); beta HCH: Н.д. (not detected); Endrin: Н.д. (not detected); Chlorpyriphos-methyl: Н.д. (not detected); Chlorpyrifos (Chlorpyriphos-ethyl): Н.д. (not detected); Heptachlor (sum of Heptachlor + Heptachlor epoxide): Н.д. (not detected); Endosulfan (alpha, beta and endosulfan sulfate): Н.д. (not detected); Deltamethrin: Н.д. (not detected); Chlordane (sum of cis- and trans-chlordane): Н.д. (not detected); Metoxychlor: Н.д. (not detected); Heptachlor epoxide: Н.д. (not detected); Endrin aldehyde: Н.д. (not detected); alpha Endosulfan: Н.д. (not detected); beta Endosulfan: Н.д. (not detected); Endrin keton: Н.д. (not detected); trans-Chlordane: Н.д. (not detected); cis-Chlordane: Н.д. (not detected); Dieldrin: Н.д. (not detected); Heptachlor: Н.д. (not detected); Endosulfan sulfate: Н.д. (not detected)</t>
         </is>
@@ -5224,7 +5227,7 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0034</t>
+          <t>CoQ-PP-2026-0039</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -5232,27 +5235,27 @@
           <t>CJ082501/1</t>
         </is>
       </c>
-      <c r="E15" s="19" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>P060022</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>CJ_THC22.5:CBD1</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t>R1 · Jan–Feb 2026</t>
         </is>
       </c>
-      <c r="I15" s="23" t="inlineStr">
+      <c r="I15" s="19" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -5262,7 +5265,7 @@
           <t>PP CoA #041, 20.02.2026, PP</t>
         </is>
       </c>
-      <c r="K15" s="23" t="inlineStr">
+      <c r="K15" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -5272,7 +5275,7 @@
           <t>iCoA-PP-2026-0060 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="M15" s="23" t="inlineStr">
+      <c r="M15" s="19" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -5285,7 +5288,7 @@
       <c r="O15" s="27" t="n">
         <v>24.96</v>
       </c>
-      <c r="P15" s="23" t="inlineStr">
+      <c r="P15" s="19" t="inlineStr">
         <is>
           <t>Grade II, 19.75 – 25.25</t>
         </is>
@@ -5313,7 +5316,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V15" s="23" t="inlineStr">
+      <c r="V15" s="19" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -5331,7 +5334,7 @@
           <t>ППК26002, 21.01.2026, CNP</t>
         </is>
       </c>
-      <c r="Z15" s="23" t="inlineStr">
+      <c r="Z15" s="19" t="inlineStr">
         <is>
           <t>1.5×10^2</t>
         </is>
@@ -5341,7 +5344,7 @@
           <t>8/0011/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AB15" s="23" t="inlineStr">
+      <c r="AB15" s="19" t="inlineStr">
         <is>
           <t>1.3×10^2</t>
         </is>
@@ -5351,7 +5354,7 @@
           <t>8/0011/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AD15" s="23" t="inlineStr">
+      <c r="AD15" s="19" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -5361,7 +5364,7 @@
           <t>8/0011/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AF15" s="23" t="inlineStr">
+      <c r="AF15" s="19" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -5371,7 +5374,7 @@
           <t>8/0011/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AH15" s="23" t="inlineStr">
+      <c r="AH15" s="19" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -5391,7 +5394,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL15" s="23" t="inlineStr">
+      <c r="AL15" s="19" t="inlineStr">
         <is>
           <t>&lt;2</t>
         </is>
@@ -5419,7 +5422,7 @@
           <t>81/2026, 02.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AR15" s="23" t="inlineStr">
+      <c r="AR15" s="19" t="inlineStr">
         <is>
           <t>Н.д.</t>
         </is>
@@ -5429,7 +5432,7 @@
           <t>81/2026, 02.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AT15" s="23" t="inlineStr">
+      <c r="AT15" s="19" t="inlineStr">
         <is>
           <t>Н.д.</t>
         </is>
@@ -5439,7 +5442,7 @@
           <t>81/2026, 02.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AV15" s="23" t="inlineStr">
+      <c r="AV15" s="19" t="inlineStr">
         <is>
           <t>Н.д.</t>
         </is>
@@ -5449,7 +5452,7 @@
           <t>81/2026, 02.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AX15" s="23" t="inlineStr">
+      <c r="AX15" s="19" t="inlineStr">
         <is>
           <t>Lindan (Gama HCH): Н.д. (not detected); Aldrin: Н.д. (not detected); Dieldrin i Aldrin (expressed as Dieldrin): Н.д. (not detected); HCB (Hexachlorobenzene): Н.д. (not detected); 4,4' DDE: Н.д. (not detected); 4,4' DDD: Н.д. (not detected); 4,4' DDT: Н.д. (not detected); Vkupno DDT (Total DDT): Н.д. (not detected); delta HCH: Н.д. (not detected); alpha HCH: Н.д. (not detected); beta HCH: Н.д. (not detected); Endrin: Н.д. (not detected); Chlorpyriphos-methyl: Н.д. (not detected); Chlorpyrifos (Chlorpyriphos-ethyl): Н.д. (not detected); Heptachlor (sum of Heptachlor + Heptachlor epoxide): Н.д. (not detected); Endosulfan (alpha, beta and endosulfan sulfate): Н.д. (not detected); Deltamethrin: Н.д. (not detected); Chlordane (sum of cis- and trans-chlordane): Н.д. (not detected); Metoxychlor: Н.д. (not detected); Heptachlor epoxide: Н.д. (not detected); Endrin aldehyde: Н.д. (not detected); alpha Endosulfan: Н.д. (not detected); beta Endosulfan: Н.д. (not detected); Endrin keton: Н.д. (not detected); trans-Chlordane: Н.д. (not detected); cis-Chlordane: Н.д. (not detected); Dieldrin: Н.д. (not detected); Heptachlor: Н.д. (not detected); Endosulfan sulfate: Н.д. (not detected)</t>
         </is>
@@ -5471,7 +5474,7 @@
       </c>
       <c r="C16" s="31" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0036</t>
+          <t>CoQ-PP-2026-0034</t>
         </is>
       </c>
       <c r="D16" s="32" t="inlineStr">
@@ -5479,27 +5482,27 @@
           <t>GP082501/1</t>
         </is>
       </c>
-      <c r="E16" s="31" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>P050312</t>
         </is>
       </c>
-      <c r="F16" s="33" t="inlineStr">
+      <c r="F16" s="34" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
       </c>
-      <c r="G16" s="33" t="inlineStr">
+      <c r="G16" s="34" t="inlineStr">
         <is>
           <t>GP_THC20:CBD1</t>
         </is>
       </c>
-      <c r="H16" s="34" t="inlineStr">
+      <c r="H16" s="35" t="inlineStr">
         <is>
           <t>R1 · Dec 2025 – Jan 2026</t>
         </is>
       </c>
-      <c r="I16" s="35" t="inlineStr">
+      <c r="I16" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -5509,7 +5512,7 @@
           <t>iCoA-PP-2026-0063 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K16" s="35" t="inlineStr">
+      <c r="K16" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -5532,7 +5535,7 @@
       <c r="O16" s="39" t="n">
         <v>21.29</v>
       </c>
-      <c r="P16" s="35" t="inlineStr">
+      <c r="P16" s="31" t="inlineStr">
         <is>
           <t>Grade III, 18.00 – 22.00</t>
         </is>
@@ -5560,7 +5563,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V16" s="35" t="inlineStr">
+      <c r="V16" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -5578,7 +5581,7 @@
           <t>PP CoA #020 / ППК25380, 21.01.2026, CNP</t>
         </is>
       </c>
-      <c r="Z16" s="35" t="inlineStr">
+      <c r="Z16" s="31" t="inlineStr">
         <is>
           <t>4.3×10^2</t>
         </is>
@@ -5588,7 +5591,7 @@
           <t>1226/2192/25, Issued Dec 2025, IPH</t>
         </is>
       </c>
-      <c r="AB16" s="35" t="inlineStr">
+      <c r="AB16" s="31" t="inlineStr">
         <is>
           <t>1×10^3</t>
         </is>
@@ -5598,7 +5601,7 @@
           <t>1226/2192/25, Issued Dec 2025, IPH</t>
         </is>
       </c>
-      <c r="AD16" s="35" t="inlineStr">
+      <c r="AD16" s="31" t="inlineStr">
         <is>
           <t>&lt; 10^3 and &gt; 10^2</t>
         </is>
@@ -5608,7 +5611,7 @@
           <t>1226/2192/25, Issued Dec 2025, IPH</t>
         </is>
       </c>
-      <c r="AF16" s="35" t="inlineStr">
+      <c r="AF16" s="31" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -5618,7 +5621,7 @@
           <t>1226/2192/25, Issued Dec 2025, IPH</t>
         </is>
       </c>
-      <c r="AH16" s="35" t="inlineStr">
+      <c r="AH16" s="31" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -5638,7 +5641,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL16" s="35" t="inlineStr">
+      <c r="AL16" s="31" t="inlineStr">
         <is>
           <t>&lt;2</t>
         </is>
@@ -5690,7 +5693,7 @@
           <t>5888/2025, 12.12.2025, IPH</t>
         </is>
       </c>
-      <c r="AX16" s="35" t="inlineStr">
+      <c r="AX16" s="31" t="inlineStr">
         <is>
           <t>Lindan (Gama HCH): Н.д. (not detected); Aldrin: Н.д. (not detected); Dieldrin i Aldrin (expressed as Dieldrin): Н.д. (not detected); HCB (Hexachlorobenzene): Н.д. (not detected); 4,4' DDE: Н.д. (not detected); 4,4' DDD: Н.д. (not detected); 4,4' DDT: Н.д. (not detected); Vkupno DDT (Total DDT): Н.д. (not detected); delta HCH: Н.д. (not detected); alpha HCH: Н.д. (not detected); beta HCH: Н.д. (not detected); Endrin: Н.д. (not detected); Chlorpyriphos-methyl: Н.д. (not detected); Chlorpyrifos (Chlorpyriphos-ethyl): Н.д. (not detected); Heptachlor (sum of Heptachlor + Heptachlor epoxide): Н.д. (not detected); Endosulfan (alpha, beta and endosulfan sulfate): Н.д. (not detected); Deltamethrin: Н.д. (not detected); Chlordane (sum of cis- and trans-chlordane): Н.д. (not detected); Metoxychlor: Н.д. (not detected); Heptachlor epoxide: Н.д. (not detected); Endrin aldehyde: Н.д. (not detected); alpha Endosulfan: Н.д. (not detected); beta Endosulfan: Н.д. (not detected); Endrin keton: Н.д. (not detected); trans-Chlordane: Н.д. (not detected); cis-Chlordane: Н.д. (not detected); Dieldrin: Н.д. (not detected); Heptachlor: Н.д. (not detected); Endosulfan sulfate: Н.д. (not detected)</t>
         </is>
@@ -5712,7 +5715,7 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0038</t>
+          <t>CoQ-PP-2026-0041</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -5720,27 +5723,27 @@
           <t>WC082501</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>P060012</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>Wedding Crasher</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>WC_THC22.5:CBD1</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t>R1 · Jan–Feb 2026</t>
         </is>
       </c>
-      <c r="I17" s="23" t="inlineStr">
+      <c r="I17" s="19" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -5750,7 +5753,7 @@
           <t>PP CoA #035, 20.02.2026, PP</t>
         </is>
       </c>
-      <c r="K17" s="23" t="inlineStr">
+      <c r="K17" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -5760,7 +5763,7 @@
           <t>iCoA-PP-2026-0066 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="M17" s="23" t="inlineStr">
+      <c r="M17" s="19" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -5773,7 +5776,7 @@
       <c r="O17" s="27" t="n">
         <v>21.67</v>
       </c>
-      <c r="P17" s="23" t="inlineStr">
+      <c r="P17" s="19" t="inlineStr">
         <is>
           <t>Grade II, 20.00 – 25.00</t>
         </is>
@@ -5801,7 +5804,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V17" s="23" t="inlineStr">
+      <c r="V17" s="19" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -5835,7 +5838,7 @@
           <t>3/0006/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AD17" s="23" t="inlineStr">
+      <c r="AD17" s="19" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -5845,7 +5848,7 @@
           <t>3/0006/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AF17" s="23" t="inlineStr">
+      <c r="AF17" s="19" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -5855,7 +5858,7 @@
           <t>3/0006/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AH17" s="23" t="inlineStr">
+      <c r="AH17" s="19" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -5875,7 +5878,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL17" s="23" t="inlineStr">
+      <c r="AL17" s="19" t="inlineStr">
         <is>
           <t>&lt;2</t>
         </is>
@@ -5895,7 +5898,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AP17" s="23" t="inlineStr">
+      <c r="AP17" s="19" t="inlineStr">
         <is>
           <t>Н.д.</t>
         </is>
@@ -5905,7 +5908,7 @@
           <t>80/2026, 02.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AR17" s="23" t="inlineStr">
+      <c r="AR17" s="19" t="inlineStr">
         <is>
           <t>Н.д.</t>
         </is>
@@ -5915,7 +5918,7 @@
           <t>80/2026, 02.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AT17" s="23" t="inlineStr">
+      <c r="AT17" s="19" t="inlineStr">
         <is>
           <t>Н.д.</t>
         </is>
@@ -5925,7 +5928,7 @@
           <t>80/2026, 02.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AV17" s="23" t="inlineStr">
+      <c r="AV17" s="19" t="inlineStr">
         <is>
           <t>Н.д.</t>
         </is>
@@ -5935,7 +5938,7 @@
           <t>80/2026, 02.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AX17" s="23" t="inlineStr">
+      <c r="AX17" s="19" t="inlineStr">
         <is>
           <t>Lindan (Gama HCH): Н.д. (not detected); Aldrin: Н.д. (not detected); Dieldrin i Aldrin (expressed as Dieldrin): Н.д. (not detected); HCB (Hexachlorobenzene): Н.д. (not detected); 4,4' DDE: Н.д. (not detected); 4,4' DDD: Н.д. (not detected); 4,4' DDT: Н.д. (not detected); Vkupno DDT (Total DDT): Н.д. (not detected); delta HCH: Н.д. (not detected); alpha HCH: Н.д. (not detected); beta HCH: Н.д. (not detected); Endrin: Н.д. (not detected); Chlorpyriphos-methyl: Н.д. (not detected); Chlorpyrifos (Chlorpyriphos-ethyl): Н.д. (not detected); Heptachlor (sum of Heptachlor + Heptachlor epoxide): Н.д. (not detected); Endosulfan (alpha, beta and endosulfan sulfate): Н.д. (not detected); Deltamethrin: Н.д. (not detected); Chlordane (sum of cis- and trans-chlordane): Н.д. (not detected); Metoxychlor: Н.д. (not detected); Heptachlor epoxide: Н.д. (not detected); Endrin aldehyde: Н.д. (not detected); alpha Endosulfan: Н.д. (not detected); beta Endosulfan: Н.д. (not detected); Endrin keton: Н.д. (not detected); trans-Chlordane: Н.д. (not detected); cis-Chlordane: Н.д. (not detected); Dieldrin: Н.д. (not detected); Heptachlor: Н.д. (not detected); Endosulfan sulfate: Н.д. (not detected)</t>
         </is>
@@ -5957,7 +5960,7 @@
       </c>
       <c r="C18" s="31" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0040</t>
+          <t>CoQ-PP-2026-0042</t>
         </is>
       </c>
       <c r="D18" s="32" t="inlineStr">
@@ -5965,27 +5968,27 @@
           <t>CJ092501</t>
         </is>
       </c>
-      <c r="E18" s="31" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>P060072</t>
         </is>
       </c>
-      <c r="F18" s="33" t="inlineStr">
+      <c r="F18" s="34" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
       </c>
-      <c r="G18" s="33" t="inlineStr">
+      <c r="G18" s="34" t="inlineStr">
         <is>
           <t>CJ_THC22.5:CBD1</t>
         </is>
       </c>
-      <c r="H18" s="34" t="inlineStr">
+      <c r="H18" s="35" t="inlineStr">
         <is>
           <t>R1 · Jan–Feb 2026</t>
         </is>
       </c>
-      <c r="I18" s="35" t="inlineStr">
+      <c r="I18" s="31" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -5995,7 +5998,7 @@
           <t>PP CoA #039, 20.02.2026, PP</t>
         </is>
       </c>
-      <c r="K18" s="35" t="inlineStr">
+      <c r="K18" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -6005,7 +6008,7 @@
           <t>iCoA-PP-2026-0069 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="M18" s="35" t="inlineStr">
+      <c r="M18" s="31" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -6018,7 +6021,7 @@
       <c r="O18" s="39" t="n">
         <v>22.3</v>
       </c>
-      <c r="P18" s="35" t="inlineStr">
+      <c r="P18" s="31" t="inlineStr">
         <is>
           <t>Grade II, 19.75 – 25.25</t>
         </is>
@@ -6046,7 +6049,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V18" s="35" t="inlineStr">
+      <c r="V18" s="31" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -6064,7 +6067,7 @@
           <t>ППК26007, 21.01.2026, CNP</t>
         </is>
       </c>
-      <c r="Z18" s="35" t="inlineStr">
+      <c r="Z18" s="31" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -6074,7 +6077,7 @@
           <t>10/0013/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AB18" s="35" t="inlineStr">
+      <c r="AB18" s="31" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -6084,7 +6087,7 @@
           <t>10/0013/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AD18" s="35" t="inlineStr">
+      <c r="AD18" s="31" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -6094,7 +6097,7 @@
           <t>10/0013/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AF18" s="35" t="inlineStr">
+      <c r="AF18" s="31" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -6104,7 +6107,7 @@
           <t>10/0013/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AH18" s="35" t="inlineStr">
+      <c r="AH18" s="31" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -6124,7 +6127,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL18" s="35" t="inlineStr">
+      <c r="AL18" s="31" t="inlineStr">
         <is>
           <t>&lt;2</t>
         </is>
@@ -6152,7 +6155,7 @@
           <t>86/2026, 02.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AR18" s="35" t="inlineStr">
+      <c r="AR18" s="31" t="inlineStr">
         <is>
           <t>Н.д.</t>
         </is>
@@ -6162,7 +6165,7 @@
           <t>86/2026, 02.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AT18" s="35" t="inlineStr">
+      <c r="AT18" s="31" t="inlineStr">
         <is>
           <t>Н.д.</t>
         </is>
@@ -6180,7 +6183,7 @@
           <t>86/2026, 02.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AX18" s="35" t="inlineStr">
+      <c r="AX18" s="31" t="inlineStr">
         <is>
           <t>Lindan (Gama HCH): Н.д. (not detected); Aldrin: Н.д. (not detected); Dieldrin i Aldrin (expressed as Dieldrin): Н.д. (not detected); HCB (Hexachlorobenzene): Н.д. (not detected); 4,4' DDE: Н.д. (not detected); 4,4' DDD: Н.д. (not detected); 4,4' DDT: Н.д. (not detected); Vkupno DDT (Total DDT): Н.д. (not detected); delta HCH: Н.д. (not detected); alpha HCH: Н.д. (not detected); beta HCH: Н.д. (not detected); Endrin: Н.д. (not detected); Chlorpyriphos-methyl: Н.д. (not detected); Chlorpyrifos (Chlorpyriphos-ethyl): Н.д. (not detected); Heptachlor (sum of Heptachlor + Heptachlor epoxide): Н.д. (not detected); Endosulfan (alpha, beta and endosulfan sulfate): Н.д. (not detected); Deltamethrin: Н.д. (not detected); Chlordane (sum of cis- and trans-chlordane): Н.д. (not detected); Metoxychlor: Н.д. (not detected); Heptachlor epoxide: Н.д. (not detected); Endrin aldehyde: Н.д. (not detected); alpha Endosulfan: Н.д. (not detected); beta Endosulfan: Н.д. (not detected); Endrin keton: Н.д. (not detected); trans-Chlordane: Н.д. (not detected); cis-Chlordane: Н.д. (not detected); Dieldrin: Н.д. (not detected); Heptachlor: Н.д. (not detected); Endosulfan sulfate: Н.д. (not detected)</t>
         </is>
@@ -6202,7 +6205,7 @@
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0041</t>
+          <t>CoQ-PP-2026-0038</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -6210,27 +6213,27 @@
           <t>GP092501</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>P060092</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>GP_THC24:CBD1</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>R1 · Jan–Feb 2026</t>
         </is>
       </c>
-      <c r="I19" s="23" t="inlineStr">
+      <c r="I19" s="19" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -6240,7 +6243,7 @@
           <t>PP CoA #033, 20.02.2020 [see source], PP</t>
         </is>
       </c>
-      <c r="K19" s="23" t="inlineStr">
+      <c r="K19" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -6250,7 +6253,7 @@
           <t>iCoA-PP-2026-0070 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="M19" s="23" t="inlineStr">
+      <c r="M19" s="19" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -6263,7 +6266,7 @@
       <c r="O19" s="27" t="n">
         <v>25.73</v>
       </c>
-      <c r="P19" s="23" t="inlineStr">
+      <c r="P19" s="19" t="inlineStr">
         <is>
           <t>Grade II, 22.00 – 26.00</t>
         </is>
@@ -6291,7 +6294,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V19" s="23" t="inlineStr">
+      <c r="V19" s="19" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -6309,7 +6312,7 @@
           <t>ППК26009, 21.01.2026, CNP</t>
         </is>
       </c>
-      <c r="Z19" s="23" t="inlineStr">
+      <c r="Z19" s="19" t="inlineStr">
         <is>
           <t>1 x 10^2</t>
         </is>
@@ -6319,7 +6322,7 @@
           <t>5/0008/26, 20.01.2026 [see source], IPH</t>
         </is>
       </c>
-      <c r="AB19" s="23" t="inlineStr">
+      <c r="AB19" s="19" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -6329,7 +6332,7 @@
           <t>5/0008/26, 20.01.2026 [see source], IPH</t>
         </is>
       </c>
-      <c r="AD19" s="23" t="inlineStr">
+      <c r="AD19" s="19" t="inlineStr">
         <is>
           <t>&lt; 10^2 and &gt; 10</t>
         </is>
@@ -6339,7 +6342,7 @@
           <t>5/0008/26, 20.01.2026 [see source], IPH</t>
         </is>
       </c>
-      <c r="AF19" s="23" t="inlineStr">
+      <c r="AF19" s="19" t="inlineStr">
         <is>
           <t>Одговара (Complies/Absent)</t>
         </is>
@@ -6349,7 +6352,7 @@
           <t>5/0008/26, 20.01.2026 [see source], IPH</t>
         </is>
       </c>
-      <c r="AH19" s="23" t="inlineStr">
+      <c r="AH19" s="19" t="inlineStr">
         <is>
           <t>Одговара (Complies/Absent)</t>
         </is>
@@ -6369,7 +6372,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AL19" s="23" t="inlineStr">
+      <c r="AL19" s="19" t="inlineStr">
         <is>
           <t>&lt;2</t>
         </is>
@@ -6397,7 +6400,7 @@
           <t>88/2026, 03.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AR19" s="23" t="inlineStr">
+      <c r="AR19" s="19" t="inlineStr">
         <is>
           <t>н.д.</t>
         </is>
@@ -6407,7 +6410,7 @@
           <t>88/2026, 03.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AT19" s="23" t="inlineStr">
+      <c r="AT19" s="19" t="inlineStr">
         <is>
           <t>н.д.</t>
         </is>
@@ -6425,7 +6428,7 @@
           <t>88/2026, 03.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AX19" s="23" t="inlineStr">
+      <c r="AX19" s="19" t="inlineStr">
         <is>
           <t>Lindan (Gama HCH): н.д.; Aldrin: н.д.; Dieldrin и Aldrin (expressed as Dieldrin): н.д.; HCB: н.д.; 4,4' DDE: н.д.; 4,4' DDD: н.д.; 4,4' DDT: н.д.; вкупно DDT (total DDT): н.д.; delta HCH: н.д.; alpha HCH: н.д.; beta HCH: н.д.; Endrin: н.д.; Chlorpyrifos-methyl: н.д.; Chlorpyrifos: н.д.; Heptachlor (sum of Heptachlor + Heptachlor epoxide): н.д.; Endosulfan (alpha, beta and endosulfan sulfate): н.д.; Deltamethrin: н.д.; Chlordane (sum of cis- and trans-chlordane): н.д.; Metoxychlor: н.д.; Heptachlor epoxide: н.д.; Endrin aldehyde: н.д.; alpha Endosulfan: н.д.; beta Endosulfan: н.д.; Endrin keton: н.д.; trans-Chlordane: н.д.; cis-Chlordane: н.д.; Dieldrin: н.д.; Heptachlor: н.д.; Endosulfan sulfate: н.д.</t>
         </is>
@@ -6447,7 +6450,7 @@
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0042</t>
+          <t>CoQ-PP-2026-0043</t>
         </is>
       </c>
       <c r="D20" s="32" t="inlineStr">
@@ -6455,27 +6458,27 @@
           <t>OPM092501</t>
         </is>
       </c>
-      <c r="E20" s="31" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>P060042</t>
         </is>
       </c>
-      <c r="F20" s="33" t="inlineStr">
+      <c r="F20" s="34" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
-      <c r="G20" s="33" t="inlineStr">
+      <c r="G20" s="34" t="inlineStr">
         <is>
           <t>OPM_THC10:CBD1</t>
         </is>
       </c>
-      <c r="H20" s="34" t="inlineStr">
+      <c r="H20" s="35" t="inlineStr">
         <is>
           <t>R1 · Jan–Feb 2026</t>
         </is>
       </c>
-      <c r="I20" s="35" t="inlineStr">
+      <c r="I20" s="31" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -6485,7 +6488,7 @@
           <t>PP CoA #040, 20.02.2026, PP</t>
         </is>
       </c>
-      <c r="K20" s="35" t="inlineStr">
+      <c r="K20" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -6495,7 +6498,7 @@
           <t>iCoA-PP-2026-0071 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="M20" s="35" t="inlineStr">
+      <c r="M20" s="31" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -6508,7 +6511,7 @@
       <c r="O20" s="39" t="n">
         <v>9.43</v>
       </c>
-      <c r="P20" s="35" t="inlineStr">
+      <c r="P20" s="31" t="inlineStr">
         <is>
           <t>Grade IV, 7.09 – 13.00</t>
         </is>
@@ -6536,7 +6539,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V20" s="35" t="inlineStr">
+      <c r="V20" s="31" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -6570,7 +6573,7 @@
           <t>2/0005/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AD20" s="35" t="inlineStr">
+      <c r="AD20" s="31" t="inlineStr">
         <is>
           <t>&lt; 10^2 and &gt; 10</t>
         </is>
@@ -6580,7 +6583,7 @@
           <t>2/0005/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AF20" s="35" t="inlineStr">
+      <c r="AF20" s="31" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -6590,7 +6593,7 @@
           <t>2/0005/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AH20" s="35" t="inlineStr">
+      <c r="AH20" s="31" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -6636,7 +6639,7 @@
           <t>87/2026, 03.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AR20" s="35" t="inlineStr">
+      <c r="AR20" s="31" t="inlineStr">
         <is>
           <t>Н.д.</t>
         </is>
@@ -6646,7 +6649,7 @@
           <t>87/2026, 03.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AT20" s="35" t="inlineStr">
+      <c r="AT20" s="31" t="inlineStr">
         <is>
           <t>Н.д.</t>
         </is>
@@ -6656,7 +6659,7 @@
           <t>87/2026, 03.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AV20" s="35" t="inlineStr">
+      <c r="AV20" s="31" t="inlineStr">
         <is>
           <t>Н.д.</t>
         </is>
@@ -6666,7 +6669,7 @@
           <t>87/2026, 03.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AX20" s="35" t="inlineStr">
+      <c r="AX20" s="31" t="inlineStr">
         <is>
           <t>Lindan (Gama HCH): Н.д. (not detected); Aldrin: Н.д. (not detected); Dieldrin i Aldrin (expressed as Dieldrin): Н.д. (not detected); HCB (Hexachlorobenzene): Н.д. (not detected); 4,4' DDE: Н.д. (not detected); 4,4' DDD: Н.д. (not detected); 4,4' DDT: Н.д. (not detected); Vkupno DDT (Total DDT): Н.д. (not detected); delta HCH: Н.д. (not detected); alpha HCH: Н.д. (not detected); beta HCH: Н.д. (not detected); Endrin: Н.д. (not detected); Chlorpyriphos-methyl: Н.д. (not detected); Chlorpyrifos (Chlorpyriphos-ethyl): Н.д. (not detected); Heptachlor (sum of Heptachlor + Heptachlor epoxide): Н.д. (not detected); Endosulfan (alpha, beta and endosulfan sulfate): Н.д. (not detected); Deltamethrin: Н.д. (not detected); Chlordane (sum of cis- and trans-chlordane): Н.д. (not detected); Metoxychlor: Н.д. (not detected); Heptachlor epoxide: Н.д. (not detected); Endrin aldehyde: Н.д. (not detected); alpha Endosulfan: Н.д. (not detected); beta Endosulfan: Н.д. (not detected); Endrin keton: Н.д. (not detected); trans-Chlordane: Н.д. (not detected); cis-Chlordane: Н.д. (not detected); Dieldrin: Н.д. (not detected); Heptachlor: Н.д. (not detected); Endosulfan sulfate: Н.д. (not detected)</t>
         </is>
@@ -6688,7 +6691,7 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0044</t>
+          <t>CoQ-PP-2026-0045</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -6696,27 +6699,27 @@
           <t>SJ092501</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>P060082</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>Sleepy Joy</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>SJ_THC10.5:CBD1</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="23" t="inlineStr">
         <is>
           <t>R1 · Jan–Feb 2026</t>
         </is>
       </c>
-      <c r="I21" s="23" t="inlineStr">
+      <c r="I21" s="19" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -6726,7 +6729,7 @@
           <t>PP CoA #038, 20.02.2026, PP</t>
         </is>
       </c>
-      <c r="K21" s="23" t="inlineStr">
+      <c r="K21" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -6736,7 +6739,7 @@
           <t>iCoA-PP-2026-0073 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="M21" s="23" t="inlineStr">
+      <c r="M21" s="19" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -6749,7 +6752,7 @@
       <c r="O21" s="27" t="n">
         <v>10.96</v>
       </c>
-      <c r="P21" s="23" t="inlineStr">
+      <c r="P21" s="19" t="inlineStr">
         <is>
           <t>Grade IV, 7.75 – 13.00</t>
         </is>
@@ -6777,7 +6780,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V21" s="23" t="inlineStr">
+      <c r="V21" s="19" t="inlineStr">
         <is>
           <t>Confirms</t>
         </is>
@@ -6795,7 +6798,7 @@
           <t>ППК26006, 21.01.2026, CNP</t>
         </is>
       </c>
-      <c r="Z21" s="23" t="inlineStr">
+      <c r="Z21" s="19" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -6805,7 +6808,7 @@
           <t>9/0012/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AB21" s="23" t="inlineStr">
+      <c r="AB21" s="19" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -6815,7 +6818,7 @@
           <t>9/0012/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AD21" s="23" t="inlineStr">
+      <c r="AD21" s="19" t="inlineStr">
         <is>
           <t>&lt;10</t>
         </is>
@@ -6825,7 +6828,7 @@
           <t>9/0012/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AF21" s="23" t="inlineStr">
+      <c r="AF21" s="19" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -6835,7 +6838,7 @@
           <t>9/0012/26, 20.01.2026, IPH</t>
         </is>
       </c>
-      <c r="AH21" s="23" t="inlineStr">
+      <c r="AH21" s="19" t="inlineStr">
         <is>
           <t>Odgovara (Absent)</t>
         </is>
@@ -6881,7 +6884,7 @@
           <t>85/2026, 02.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AR21" s="23" t="inlineStr">
+      <c r="AR21" s="19" t="inlineStr">
         <is>
           <t>Н.д.</t>
         </is>
@@ -6891,7 +6894,7 @@
           <t>85/2026, 02.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AT21" s="23" t="inlineStr">
+      <c r="AT21" s="19" t="inlineStr">
         <is>
           <t>Н.д.</t>
         </is>
@@ -6909,7 +6912,7 @@
           <t>85/2026, 02.02.2026, IPH</t>
         </is>
       </c>
-      <c r="AX21" s="23" t="inlineStr">
+      <c r="AX21" s="19" t="inlineStr">
         <is>
           <t>Lindan (Gama HCH): Н.д. (not detected); Aldrin: Н.д. (not detected); Dieldrin i Aldrin (expressed as Dieldrin): Н.д. (not detected); HCB (Hexachlorobenzene): Н.д. (not detected); 4,4' DDE: Н.д. (not detected); 4,4' DDD: Н.д. (not detected); 4,4' DDT: Н.д. (not detected); Vkupno DDT (Total DDT): Н.д. (not detected); delta HCH: Н.д. (not detected); alpha HCH: Н.д. (not detected); beta HCH: Н.д. (not detected); Endrin: Н.д. (not detected); Chlorpyriphos-methyl: Н.д. (not detected); Chlorpyrifos (Chlorpyriphos-ethyl): Н.д. (not detected); Heptachlor (sum of Heptachlor + Heptachlor epoxide): Н.д. (not detected); Endosulfan (alpha, beta and endosulfan sulfate): Н.д. (not detected); Deltamethrin: Н.д. (not detected); Chlordane (sum of cis- and trans-chlordane): Н.д. (not detected); Metoxychlor: Н.д. (not detected); Heptachlor epoxide: Н.д. (not detected); Endrin aldehyde: Н.д. (not detected); alpha Endosulfan: Н.д. (not detected); beta Endosulfan: Н.д. (not detected); Endrin keton: Н.д. (not detected); trans-Chlordane: Н.д. (not detected); cis-Chlordane: Н.д. (not detected); Dieldrin: Н.д. (not detected); Heptachlor: Н.д. (not detected); Endosulfan sulfate: Н.д. (not detected)</t>
         </is>
@@ -6941,22 +6944,22 @@
           <t>ACC102501</t>
         </is>
       </c>
-      <c r="E22" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="33" t="inlineStr">
+      <c r="E22" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="34" t="inlineStr">
         <is>
           <t>Amnesia Core Cut</t>
         </is>
       </c>
-      <c r="G22" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H22" s="34" t="inlineStr">
+      <c r="G22" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="35" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -7198,22 +7201,22 @@
           <t>CF102501</t>
         </is>
       </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>Chem Flyer</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -7445,7 +7448,7 @@
       </c>
       <c r="C24" s="31" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0045</t>
+          <t>CoQ-PP-2026-0046</t>
         </is>
       </c>
       <c r="D24" s="32" t="inlineStr">
@@ -7453,27 +7456,27 @@
           <t>GRC102501/2</t>
         </is>
       </c>
-      <c r="E24" s="31" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>P060182</t>
         </is>
       </c>
-      <c r="F24" s="33" t="inlineStr">
+      <c r="F24" s="34" t="inlineStr">
         <is>
           <t>Graps &amp; Creme</t>
         </is>
       </c>
-      <c r="G24" s="33" t="inlineStr">
+      <c r="G24" s="34" t="inlineStr">
         <is>
           <t>GRC_THC12.5:CBD1</t>
         </is>
       </c>
-      <c r="H24" s="34" t="inlineStr">
+      <c r="H24" s="35" t="inlineStr">
         <is>
           <t>R1 · Mar 2026</t>
         </is>
       </c>
-      <c r="I24" s="35" t="inlineStr">
+      <c r="I24" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -7483,7 +7486,7 @@
           <t>iCoA-PP-2026-0075 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K24" s="35" t="inlineStr">
+      <c r="K24" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -7506,7 +7509,7 @@
       <c r="O24" s="39" t="n">
         <v>11.53</v>
       </c>
-      <c r="P24" s="35" t="inlineStr">
+      <c r="P24" s="31" t="inlineStr">
         <is>
           <t>Grade IV, 10.00 – 15.00</t>
         </is>
@@ -7516,7 +7519,7 @@
           <t>051-6-K/26, 04.03.2026, FARM</t>
         </is>
       </c>
-      <c r="R24" s="35" t="inlineStr">
+      <c r="R24" s="31" t="inlineStr">
         <is>
           <t>&lt; LOQ (&lt;0.20%)</t>
         </is>
@@ -7526,7 +7529,7 @@
           <t>051-6-K/26, 04.03.2026, FARM</t>
         </is>
       </c>
-      <c r="T24" s="35" t="inlineStr">
+      <c r="T24" s="31" t="inlineStr">
         <is>
           <t>&lt; LOQ</t>
         </is>
@@ -7536,7 +7539,7 @@
           <t>051-6-K/26, 04.03.2026, FARM</t>
         </is>
       </c>
-      <c r="V24" s="35" t="inlineStr">
+      <c r="V24" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -7696,7 +7699,7 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0047</t>
+          <t>CoQ-PP-2026-0048</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -7704,27 +7707,27 @@
           <t>KC102501</t>
         </is>
       </c>
-      <c r="E25" s="19" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>P060172</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>Kush Crasher</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>KC_THC17.5:CBD1</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H25" s="23" t="inlineStr">
         <is>
           <t>R1 · Mar 2026</t>
         </is>
       </c>
-      <c r="I25" s="23" t="inlineStr">
+      <c r="I25" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -7734,7 +7737,7 @@
           <t>iCoA-PP-2026-0079 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K25" s="23" t="inlineStr">
+      <c r="K25" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -7757,7 +7760,7 @@
       <c r="O25" s="27" t="n">
         <v>17.04</v>
       </c>
-      <c r="P25" s="23" t="inlineStr">
+      <c r="P25" s="19" t="inlineStr">
         <is>
           <t>Grade III, 15.00 – 20.00</t>
         </is>
@@ -7767,7 +7770,7 @@
           <t>051-4-K/26, 04.03.2026, FARM</t>
         </is>
       </c>
-      <c r="R25" s="23" t="inlineStr">
+      <c r="R25" s="19" t="inlineStr">
         <is>
           <t>&lt; LOQ (&lt;0.20%)</t>
         </is>
@@ -7777,7 +7780,7 @@
           <t>051-4-K/26, 04.03.2026, FARM</t>
         </is>
       </c>
-      <c r="T25" s="23" t="inlineStr">
+      <c r="T25" s="19" t="inlineStr">
         <is>
           <t>&lt; LOQ</t>
         </is>
@@ -7787,7 +7790,7 @@
           <t>051-4-K/26, 04.03.2026, FARM</t>
         </is>
       </c>
-      <c r="V25" s="23" t="inlineStr">
+      <c r="V25" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -7957,22 +7960,22 @@
           <t>PUM102501</t>
         </is>
       </c>
-      <c r="E26" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="33" t="inlineStr">
+      <c r="E26" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="34" t="inlineStr">
         <is>
           <t>Pure Michigen</t>
         </is>
       </c>
-      <c r="G26" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H26" s="34" t="inlineStr">
+      <c r="G26" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="35" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -8204,7 +8207,7 @@
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0055</t>
+          <t>CoQ-PP-2026-0052</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -8212,27 +8215,27 @@
           <t>PM112501</t>
         </is>
       </c>
-      <c r="E27" s="19" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>P060232</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>Permanent Marker</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>PM_THC11.5:CBD1</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H27" s="23" t="inlineStr">
         <is>
           <t>R1 · Mar 2026</t>
         </is>
       </c>
-      <c r="I27" s="23" t="inlineStr">
+      <c r="I27" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -8242,7 +8245,7 @@
           <t>iCoA-PP-2026-0095 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K27" s="23" t="inlineStr">
+      <c r="K27" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -8265,7 +8268,7 @@
       <c r="O27" s="27" t="n">
         <v>13.33</v>
       </c>
-      <c r="P27" s="23" t="inlineStr">
+      <c r="P27" s="19" t="inlineStr">
         <is>
           <t>Grade IV, 9.01 – 14.00</t>
         </is>
@@ -8293,7 +8296,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V27" s="23" t="inlineStr">
+      <c r="V27" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -8453,7 +8456,7 @@
       </c>
       <c r="C28" s="31" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0056</t>
+          <t>CoQ-PP-2026-0060</t>
         </is>
       </c>
       <c r="D28" s="32" t="inlineStr">
@@ -8461,27 +8464,27 @@
           <t>SCR112501</t>
         </is>
       </c>
-      <c r="E28" s="31" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>P060282</t>
         </is>
       </c>
-      <c r="F28" s="33" t="inlineStr">
+      <c r="F28" s="34" t="inlineStr">
         <is>
           <t>Scrambler</t>
         </is>
       </c>
-      <c r="G28" s="33" t="inlineStr">
+      <c r="G28" s="34" t="inlineStr">
         <is>
           <t>SCR_THC18.5:CBD1</t>
         </is>
       </c>
-      <c r="H28" s="34" t="inlineStr">
+      <c r="H28" s="35" t="inlineStr">
         <is>
           <t>R1 · May 2026</t>
         </is>
       </c>
-      <c r="I28" s="35" t="inlineStr">
+      <c r="I28" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -8491,7 +8494,7 @@
           <t>iCoA-PP-2026-0097 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K28" s="35" t="inlineStr">
+      <c r="K28" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -8514,7 +8517,7 @@
       <c r="O28" s="39" t="n">
         <v>17.13</v>
       </c>
-      <c r="P28" s="35" t="inlineStr">
+      <c r="P28" s="31" t="inlineStr">
         <is>
           <t>Grade III, 16.13 – 20.75</t>
         </is>
@@ -8542,7 +8545,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V28" s="35" t="inlineStr">
+      <c r="V28" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -8710,27 +8713,27 @@
           <t>FB012601/1</t>
         </is>
       </c>
-      <c r="E29" s="19" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>P060322</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>FB_THC16.5:CBD1</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="23" t="inlineStr">
         <is>
           <t>R1 · May 2026</t>
         </is>
       </c>
-      <c r="I29" s="23" t="inlineStr">
+      <c r="I29" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -8740,7 +8743,7 @@
           <t>iCoA-PP-2026-0107 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K29" s="23" t="inlineStr">
+      <c r="K29" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -8763,7 +8766,7 @@
       <c r="O29" s="27" t="n">
         <v>14.68</v>
       </c>
-      <c r="P29" s="23" t="inlineStr">
+      <c r="P29" s="19" t="inlineStr">
         <is>
           <t>Grade III, 13.68 – 19.25</t>
         </is>
@@ -8791,7 +8794,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V29" s="23" t="inlineStr">
+      <c r="V29" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -8961,22 +8964,22 @@
           <t>CC012603</t>
         </is>
       </c>
-      <c r="E30" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="33" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="34" t="inlineStr">
         <is>
           <t>CashCow</t>
         </is>
       </c>
-      <c r="G30" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H30" s="34" t="inlineStr">
+      <c r="G30" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="35" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -9218,22 +9221,22 @@
           <t>JD012603/01</t>
         </is>
       </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>Jelly Donuts</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -9465,7 +9468,7 @@
       </c>
       <c r="C32" s="31" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0068</t>
+          <t>CoQ-PP-2026-0066</t>
         </is>
       </c>
       <c r="D32" s="32" t="inlineStr">
@@ -9473,27 +9476,27 @@
           <t>JD012603/2</t>
         </is>
       </c>
-      <c r="E32" s="31" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>P060412</t>
         </is>
       </c>
-      <c r="F32" s="33" t="inlineStr">
+      <c r="F32" s="34" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
         </is>
       </c>
-      <c r="G32" s="33" t="inlineStr">
+      <c r="G32" s="34" t="inlineStr">
         <is>
           <t>JD_THC20:CBD1</t>
         </is>
       </c>
-      <c r="H32" s="34" t="inlineStr">
+      <c r="H32" s="35" t="inlineStr">
         <is>
           <t>R1 · Jun 2026</t>
         </is>
       </c>
-      <c r="I32" s="35" t="inlineStr">
+      <c r="I32" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -9503,7 +9506,7 @@
           <t>iCoA-PP-2026-0117 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K32" s="35" t="inlineStr">
+      <c r="K32" s="31" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -9513,7 +9516,7 @@
           <t>iCoA-PP-2026-0117 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="M32" s="35" t="inlineStr">
+      <c r="M32" s="31" t="inlineStr">
         <is>
           <t>Conforms / Одговара</t>
         </is>
@@ -9526,7 +9529,7 @@
       <c r="O32" s="39" t="n">
         <v>20.54</v>
       </c>
-      <c r="P32" s="35" t="inlineStr">
+      <c r="P32" s="31" t="inlineStr">
         <is>
           <t>Grade III, 18.00 – 22.00</t>
         </is>
@@ -9552,7 +9555,7 @@
           <t>ППК26113, 30.06.2026, CNP</t>
         </is>
       </c>
-      <c r="V32" s="35" t="inlineStr">
+      <c r="V32" s="31" t="inlineStr">
         <is>
           <t>/ (Conforms; no seed, no leaves &gt;1 cm)</t>
         </is>
@@ -9712,7 +9715,7 @@
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0069</t>
+          <t>CoQ-PP-2026-0067</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -9720,27 +9723,27 @@
           <t>JD012603/2V</t>
         </is>
       </c>
-      <c r="E33" s="19" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>P060422</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
         </is>
       </c>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>JD_THC15:CBD1</t>
         </is>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="H33" s="23" t="inlineStr">
         <is>
           <t>R1 · Jun 2026</t>
         </is>
       </c>
-      <c r="I33" s="23" t="inlineStr">
+      <c r="I33" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -9750,7 +9753,7 @@
           <t>iCoA-PP-2026-0118 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="K33" s="23" t="inlineStr">
+      <c r="K33" s="19" t="inlineStr">
         <is>
           <t>Conforms</t>
         </is>
@@ -9760,7 +9763,7 @@
           <t>iCoA-PP-2026-0118 (proposed), 13.08.2026, PP</t>
         </is>
       </c>
-      <c r="M33" s="23" t="inlineStr">
+      <c r="M33" s="19" t="inlineStr">
         <is>
           <t>Conforms / Одговара</t>
         </is>
@@ -9773,7 +9776,7 @@
       <c r="O33" s="27" t="n">
         <v>15.16</v>
       </c>
-      <c r="P33" s="23" t="inlineStr">
+      <c r="P33" s="19" t="inlineStr">
         <is>
           <t>Grade IV, 12.50 – 18.00</t>
         </is>
@@ -9783,7 +9786,7 @@
           <t>ППК26111, 30.06.2026, CNP</t>
         </is>
       </c>
-      <c r="R33" s="23" t="inlineStr">
+      <c r="R33" s="19" t="inlineStr">
         <is>
           <t>BLQ (below limit of quantification)</t>
         </is>
@@ -9801,7 +9804,7 @@
           <t>ППК26111, 30.06.2026, CNP</t>
         </is>
       </c>
-      <c r="V33" s="23" t="inlineStr">
+      <c r="V33" s="19" t="inlineStr">
         <is>
           <t>/ (Conforms; no seed, no leaves &gt;1 cm)</t>
         </is>
@@ -10314,6 +10317,1423 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001B3A5C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="50" customHeight="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>Proposed CoQ issuance plan — one Certificate of Quality per testing round of each batch, in results-complete chronology (the latest certificate issue date within the round; declared iCoAs excluded from the basis date). The initial round's CoQ issues on completion of the initial QC sampling; a resampling (R) round produces a superseding CoQ with a new issue date carrying the resampled parameters' new results and reusing the non-resampled results from the earlier sampling's eCoAs (time-invariant parameters such as heavy metals and pesticides — 'Carried forward' below). Supersession per QCSOP 012 v.03 §6.7 ('Supersedes [original] — reason: resampling'). Codes are proposed pending the Certificate Issuance Register (QCLB 020).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>CoQ code (proposed)</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Results complete</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Strain</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Newly tested / resampled (items)</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Carried forward (items)</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>Not covered (items)</t>
+        </is>
+      </c>
+      <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>Supersedes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0007</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>23.04.2025</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>GG1024</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Apr 2025</t>
+        </is>
+      </c>
+      <c r="H3" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="22" t="inlineStr">
+        <is>
+          <t>6, 8, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K3" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0010</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>07.05.2025</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>OPM1024_01</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>R1 · May 2025</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="22" t="inlineStr">
+        <is>
+          <t>3, 6, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0015</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>10.07.2025</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>GP0824_03</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Jun–Jul 2025</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>3, 6, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0017</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>29.07.2025</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>MB0824_05</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Jul 2025</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>3, 6, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0018</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>29.07.2025</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>OPM1024_03</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Jul 2025</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>3, 6, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0023</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>19.09.2025</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>HPA052501</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Sep 2025</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>3, 6, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0026</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>01.12.2025</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>CJ062501/1</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Oct–Dec 2025</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
+          <t>6, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="n">
+        <v>29</v>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0029</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>04.12.2025</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>BSS052501</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>Blue Sunset Sherbet</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Nov–Dec 2025</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.1, 10.3, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>6, 10.2</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0030</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>CLE072501</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>Clemosa a bud</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Nov 2025 – Jan 2026</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>3, 6, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="n">
+        <v>32</v>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0032</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>GP072501/2</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Dec 2025 – Jan 2026</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>3, 6, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="n">
+        <v>34</v>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0034</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>GP082501/1</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Dec 2025 – Jan 2026</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>3, 6, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="n">
+        <v>38</v>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0038</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>03.02.2026</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>GP092501</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Jan–Feb 2026</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>6, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="n">
+        <v>39</v>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0039</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>20.02.2026</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>CJ082501/1</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Jan–Feb 2026</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>6, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="n">
+        <v>41</v>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0041</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>20.02.2026</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>WC082501</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>Wedding Crasher</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Jan–Feb 2026</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>6, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="n">
+        <v>42</v>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0042</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>20.02.2026</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>CJ092501</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Jan–Feb 2026</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>6, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="n">
+        <v>43</v>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0043</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>20.02.2026</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>OPM092501</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Jan–Feb 2026</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>6, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="n">
+        <v>45</v>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0045</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>20.02.2026</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>SJ092501</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>Sleepy Joy</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Jan–Feb 2026</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>6, 10.1, 10.3</t>
+        </is>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="n">
+        <v>46</v>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0046</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>GRC102501/2</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Mar 2026</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>3, 9.1, 9.2, 9.3, 9.4, 9.5, 10.1, 10.2, 10.3, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="n">
+        <v>48</v>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0048</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>KC102501</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>Kush Crasher</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Mar 2026</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>3, 9.1, 9.2, 9.3, 9.4, 9.5, 10.1, 10.2, 10.3, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="n">
+        <v>52</v>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0052</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>PM112501</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+      <c r="G22" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Mar 2026</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 4, 5, 7, 8</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>3, 6, 9.1, 9.2, 9.3, 9.4, 9.5, 10.1, 10.2, 10.3, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0060</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>SCR112501</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="G23" s="18" t="inlineStr">
+        <is>
+          <t>R1 · May 2026</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 4, 5, 7, 8</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>3, 6, 9.1, 9.2, 9.3, 9.4, 9.5, 10.1, 10.2, 10.3, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>61</v>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0061</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>FB012601/1</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>R1 · May 2026</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 4, 5, 7, 8</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>3, 6, 9.1, 9.2, 9.3, 9.4, 9.5, 10.1, 10.2, 10.3, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0066</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>JD012603/2</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Jun 2026</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>9.1, 9.2, 9.3, 9.4, 9.5, 10.1, 10.2, 10.3, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="n">
+        <v>67</v>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>CoQ-PP-2026-0067</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>JD012603/2V</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>R1 · Jun 2026</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>9.1, 9.2, 9.3, 9.4, 9.5, 10.1, 10.2, 10.3, 11.1, 11.2, 11.3, 11.4, 12</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:K26"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00C9A227"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -10390,12 +11810,12 @@
       <c r="A3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0005</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Foreign Matter (prior to final QC sampling)</t>
         </is>
@@ -10410,17 +11830,17 @@
           <t>2024-08</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>GP0824_03</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" s="21" t="inlineStr">
         <is>
           <t>P050072</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -10435,12 +11855,12 @@
       <c r="A4" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0006</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -10455,17 +11875,17 @@
           <t>2024-08</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t>GP0824_03</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
+      <c r="G4" s="21" t="inlineStr">
         <is>
           <t>P050072</t>
         </is>
       </c>
-      <c r="H4" s="19" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -10480,12 +11900,12 @@
       <c r="A5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0009</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Foreign Matter (prior to final QC sampling)</t>
         </is>
@@ -10500,17 +11920,17 @@
           <t>2024-08</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>MB0824_05</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>P050112</t>
         </is>
       </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>Motor Breath</t>
         </is>
@@ -10525,12 +11945,12 @@
       <c r="A6" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0010</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -10545,17 +11965,17 @@
           <t>2024-08</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>MB0824_05</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>P050112</t>
         </is>
       </c>
-      <c r="H6" s="19" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>Motor Breath</t>
         </is>
@@ -10570,12 +11990,12 @@
       <c r="A7" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0019</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -10590,17 +12010,17 @@
           <t>2024-10</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>GG1024</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>Gorilla Glue</t>
         </is>
@@ -10615,12 +12035,12 @@
       <c r="A8" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0028</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Foreign Matter (prior to final QC sampling)</t>
         </is>
@@ -10635,17 +12055,17 @@
           <t>2024-10</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>OPM1024_01</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>P050042</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
@@ -10660,12 +12080,12 @@
       <c r="A9" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0029</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -10680,17 +12100,17 @@
           <t>2024-10</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>OPM1024_01</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>P050042</t>
         </is>
       </c>
-      <c r="H9" s="19" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
@@ -10705,12 +12125,12 @@
       <c r="A10" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0032</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>Foreign Matter (prior to final QC sampling)</t>
         </is>
@@ -10725,17 +12145,17 @@
           <t>2024-10</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>OPM1024_03</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>P050082</t>
         </is>
       </c>
-      <c r="H10" s="19" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
@@ -10750,12 +12170,12 @@
       <c r="A11" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0033</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -10770,17 +12190,17 @@
           <t>2024-10</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>OPM1024_03</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>P050082</t>
         </is>
       </c>
-      <c r="H11" s="19" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
@@ -10795,12 +12215,12 @@
       <c r="A12" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0034</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -10815,17 +12235,17 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>BSS052501</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>P050192</t>
         </is>
       </c>
-      <c r="H12" s="19" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>Blue Sunset Sherbet</t>
         </is>
@@ -10840,12 +12260,12 @@
       <c r="A13" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0041</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>Foreign Matter (prior to final QC sampling)</t>
         </is>
@@ -10860,17 +12280,17 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>HPA052501</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>P050182</t>
         </is>
       </c>
-      <c r="H13" s="19" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>High Pro Amnesia</t>
         </is>
@@ -10885,12 +12305,12 @@
       <c r="A14" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0042</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -10905,17 +12325,17 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>HPA052501</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>P050182</t>
         </is>
       </c>
-      <c r="H14" s="19" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>High Pro Amnesia</t>
         </is>
@@ -10930,12 +12350,12 @@
       <c r="A15" s="18" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0045</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>Foreign Matter (prior to final QC sampling)</t>
         </is>
@@ -10950,17 +12370,17 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>CJ062501/1</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>P050222</t>
         </is>
       </c>
-      <c r="H15" s="19" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
@@ -10975,12 +12395,12 @@
       <c r="A16" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0046</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -10995,17 +12415,17 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>CJ062501/1</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>P050222</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
@@ -11020,12 +12440,12 @@
       <c r="A17" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0051</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>Foreign Matter (prior to final QC sampling)</t>
         </is>
@@ -11040,17 +12460,17 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>CLE072501</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>P050282</t>
         </is>
       </c>
-      <c r="H17" s="19" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>Clemosa a bud</t>
         </is>
@@ -11065,12 +12485,12 @@
       <c r="A18" s="18" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0052</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -11085,17 +12505,17 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>CLE072501</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>P050282</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>Clemosa a bud</t>
         </is>
@@ -11110,12 +12530,12 @@
       <c r="A19" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0055</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>Foreign Matter (prior to final QC sampling)</t>
         </is>
@@ -11130,17 +12550,17 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>GP072501/2</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>P050302</t>
         </is>
       </c>
-      <c r="H19" s="19" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -11155,12 +12575,12 @@
       <c r="A20" s="18" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0056</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -11175,17 +12595,17 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>GP072501/2</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>P050302</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -11200,12 +12620,12 @@
       <c r="A21" s="18" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0060</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -11220,17 +12640,17 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>CJ082501/1</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>P060022</t>
         </is>
       </c>
-      <c r="H21" s="19" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
@@ -11245,12 +12665,12 @@
       <c r="A22" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0062</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>Foreign Matter (prior to final QC sampling)</t>
         </is>
@@ -11265,17 +12685,17 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>GP082501/1</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>P050312</t>
         </is>
       </c>
-      <c r="H22" s="19" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -11290,12 +12710,12 @@
       <c r="A23" s="18" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0063</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -11310,17 +12730,17 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>GP082501/1</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>P050312</t>
         </is>
       </c>
-      <c r="H23" s="19" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -11335,12 +12755,12 @@
       <c r="A24" s="18" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0066</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -11355,17 +12775,17 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>WC082501</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>P060012</t>
         </is>
       </c>
-      <c r="H24" s="19" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>Wedding Crasher</t>
         </is>
@@ -11380,12 +12800,12 @@
       <c r="A25" s="18" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0069</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -11400,17 +12820,17 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>CJ092501</t>
         </is>
       </c>
-      <c r="G25" s="19" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>P060072</t>
         </is>
       </c>
-      <c r="H25" s="19" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>Cap Junky</t>
         </is>
@@ -11425,12 +12845,12 @@
       <c r="A26" s="18" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0070</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -11445,17 +12865,17 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>GP092501</t>
         </is>
       </c>
-      <c r="G26" s="19" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>P060092</t>
         </is>
       </c>
-      <c r="H26" s="19" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>Grape Pie</t>
         </is>
@@ -11470,12 +12890,12 @@
       <c r="A27" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0071</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -11490,17 +12910,17 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="F27" s="19" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>OPM092501</t>
         </is>
       </c>
-      <c r="G27" s="19" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>P060042</t>
         </is>
       </c>
-      <c r="H27" s="19" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>Orange Punch Mimosa</t>
         </is>
@@ -11515,12 +12935,12 @@
       <c r="A28" s="18" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0073</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -11535,17 +12955,17 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>SJ092501</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>P060082</t>
         </is>
       </c>
-      <c r="H28" s="19" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>Sleepy Joy</t>
         </is>
@@ -11560,12 +12980,12 @@
       <c r="A29" s="18" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0074</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>Foreign Matter (prior to final QC sampling)</t>
         </is>
@@ -11580,17 +13000,17 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>GRC102501/2</t>
         </is>
       </c>
-      <c r="G29" s="19" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>P060182</t>
         </is>
       </c>
-      <c r="H29" s="19" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>Graps &amp; Creme</t>
         </is>
@@ -11605,12 +13025,12 @@
       <c r="A30" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0075</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -11625,17 +13045,17 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="F30" s="19" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>GRC102501/2</t>
         </is>
       </c>
-      <c r="G30" s="19" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>P060182</t>
         </is>
       </c>
-      <c r="H30" s="19" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>Graps &amp; Creme</t>
         </is>
@@ -11650,12 +13070,12 @@
       <c r="A31" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0078</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>Foreign Matter (prior to final QC sampling)</t>
         </is>
@@ -11670,17 +13090,17 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>KC102501</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>P060172</t>
         </is>
       </c>
-      <c r="H31" s="19" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>Kush Crasher</t>
         </is>
@@ -11695,12 +13115,12 @@
       <c r="A32" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="19" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0079</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -11715,17 +13135,17 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>KC102501</t>
         </is>
       </c>
-      <c r="G32" s="19" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>P060172</t>
         </is>
       </c>
-      <c r="H32" s="19" t="inlineStr">
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>Kush Crasher</t>
         </is>
@@ -11740,12 +13160,12 @@
       <c r="A33" s="18" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="19" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0094</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>Foreign Matter (prior to final QC sampling)</t>
         </is>
@@ -11760,17 +13180,17 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="F33" s="19" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>PM112501</t>
         </is>
       </c>
-      <c r="G33" s="19" t="inlineStr">
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>P060232</t>
         </is>
       </c>
-      <c r="H33" s="19" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>Permanent Marker</t>
         </is>
@@ -11785,12 +13205,12 @@
       <c r="A34" s="18" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0095</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -11805,17 +13225,17 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="F34" s="19" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>PM112501</t>
         </is>
       </c>
-      <c r="G34" s="19" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>P060232</t>
         </is>
       </c>
-      <c r="H34" s="19" t="inlineStr">
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>Permanent Marker</t>
         </is>
@@ -11830,12 +13250,12 @@
       <c r="A35" s="18" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="19" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0096</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>Foreign Matter (prior to final QC sampling)</t>
         </is>
@@ -11850,17 +13270,17 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>SCR112501</t>
         </is>
       </c>
-      <c r="G35" s="19" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>P060282</t>
         </is>
       </c>
-      <c r="H35" s="19" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>Scrambler</t>
         </is>
@@ -11875,12 +13295,12 @@
       <c r="A36" s="18" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="19" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0097</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -11895,17 +13315,17 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="F36" s="19" t="inlineStr">
+      <c r="F36" s="21" t="inlineStr">
         <is>
           <t>SCR112501</t>
         </is>
       </c>
-      <c r="G36" s="19" t="inlineStr">
+      <c r="G36" s="21" t="inlineStr">
         <is>
           <t>P060282</t>
         </is>
       </c>
-      <c r="H36" s="19" t="inlineStr">
+      <c r="H36" s="21" t="inlineStr">
         <is>
           <t>Scrambler</t>
         </is>
@@ -11920,12 +13340,12 @@
       <c r="A37" s="18" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="19" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0106</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>Foreign Matter (prior to final QC sampling)</t>
         </is>
@@ -11940,17 +13360,17 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="F37" s="19" t="inlineStr">
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>FB012601/1</t>
         </is>
       </c>
-      <c r="G37" s="19" t="inlineStr">
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>P060322</t>
         </is>
       </c>
-      <c r="H37" s="19" t="inlineStr">
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
         </is>
@@ -11965,12 +13385,12 @@
       <c r="A38" s="18" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="19" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0107</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -11985,17 +13405,17 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="F38" s="19" t="inlineStr">
+      <c r="F38" s="21" t="inlineStr">
         <is>
           <t>FB012601/1</t>
         </is>
       </c>
-      <c r="G38" s="19" t="inlineStr">
+      <c r="G38" s="21" t="inlineStr">
         <is>
           <t>P060322</t>
         </is>
       </c>
-      <c r="H38" s="19" t="inlineStr">
+      <c r="H38" s="21" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
         </is>
@@ -12010,12 +13430,12 @@
       <c r="A39" s="18" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="19" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0117</t>
         </is>
       </c>
-      <c r="C39" s="21" t="inlineStr">
+      <c r="C39" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -12030,17 +13450,17 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="F39" s="19" t="inlineStr">
+      <c r="F39" s="21" t="inlineStr">
         <is>
           <t>JD012603/2</t>
         </is>
       </c>
-      <c r="G39" s="19" t="inlineStr">
+      <c r="G39" s="21" t="inlineStr">
         <is>
           <t>P060412</t>
         </is>
       </c>
-      <c r="H39" s="19" t="inlineStr">
+      <c r="H39" s="21" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
         </is>
@@ -12055,12 +13475,12 @@
       <c r="A40" s="18" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="19" t="inlineStr">
+      <c r="B40" s="21" t="inlineStr">
         <is>
           <t>iCoA-PP-2026-0118</t>
         </is>
       </c>
-      <c r="C40" s="21" t="inlineStr">
+      <c r="C40" s="22" t="inlineStr">
         <is>
           <t>Macroscopic + Microscopic ID (after final QC sampling)</t>
         </is>
@@ -12075,17 +13495,17 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="F40" s="19" t="inlineStr">
+      <c r="F40" s="21" t="inlineStr">
         <is>
           <t>JD012603/2V</t>
         </is>
       </c>
-      <c r="G40" s="19" t="inlineStr">
+      <c r="G40" s="21" t="inlineStr">
         <is>
           <t>P060422</t>
         </is>
       </c>
-      <c r="H40" s="19" t="inlineStr">
+      <c r="H40" s="21" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
         </is>
@@ -12106,7 +13526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00E9EEF5"/>
@@ -12169,7 +13589,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>1217/2168/25</t>
         </is>
@@ -12192,12 +13612,12 @@
       <c r="E2" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="21" t="inlineStr">
+      <c r="F2" s="22" t="inlineStr">
         <is>
           <t>CJ062501/1</t>
         </is>
       </c>
-      <c r="G2" s="21" t="inlineStr">
+      <c r="G2" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -12209,7 +13629,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>5661/2025</t>
         </is>
@@ -12232,12 +13652,12 @@
       <c r="E3" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>BSS052501</t>
         </is>
       </c>
-      <c r="G3" s="21" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t>11.1, 11.2, 11.3, 11.4</t>
         </is>
@@ -12249,7 +13669,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>80/2026</t>
         </is>
@@ -12272,12 +13692,12 @@
       <c r="E4" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>WC082501</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="G4" s="22" t="inlineStr">
         <is>
           <t>10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -12289,7 +13709,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>81/2026</t>
         </is>
@@ -12312,12 +13732,12 @@
       <c r="E5" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>CJ082501/1</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -12329,7 +13749,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>85/2026</t>
         </is>
@@ -12352,12 +13772,12 @@
       <c r="E6" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>SJ092501</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -12369,7 +13789,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>86/2026</t>
         </is>
@@ -12392,12 +13812,12 @@
       <c r="E7" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>CJ092501</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -12409,7 +13829,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>051-4-GS/26</t>
         </is>
@@ -12432,12 +13852,12 @@
       <c r="E8" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>KC102501</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -12449,7 +13869,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>051-6-GS/26</t>
         </is>
@@ -12472,12 +13892,12 @@
       <c r="E9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>GRC102501/2</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -12489,7 +13909,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>628/1129/25</t>
         </is>
@@ -12512,12 +13932,12 @@
       <c r="E10" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>GP0824_03</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -12529,7 +13949,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>5700/2025</t>
         </is>
@@ -12552,12 +13972,12 @@
       <c r="E11" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>CLE072501</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -12569,7 +13989,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>87/2026</t>
         </is>
@@ -12592,12 +14012,12 @@
       <c r="E12" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>OPM092501</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -12609,7 +14029,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>88/2026</t>
         </is>
@@ -12632,12 +14052,12 @@
       <c r="E13" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>GP092501</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -12649,7 +14069,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>051-4-K/26</t>
         </is>
@@ -12672,12 +14092,12 @@
       <c r="E14" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>KC102501</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>4, 5, 6</t>
         </is>
@@ -12689,7 +14109,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>051-6-K/26</t>
         </is>
@@ -12712,12 +14132,12 @@
       <c r="E15" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>GRC102501/2</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>4, 5, 6</t>
         </is>
@@ -12729,7 +14149,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>276-31-М/25</t>
         </is>
@@ -12752,12 +14172,12 @@
       <c r="E16" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>BSS052501</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>10.1, 10.3</t>
         </is>
@@ -12769,7 +14189,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>PP CoA #017</t>
         </is>
@@ -12792,12 +14212,12 @@
       <c r="E17" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>BSS052501</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>1, 7</t>
         </is>
@@ -12809,7 +14229,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>ППК26030</t>
         </is>
@@ -12832,12 +14252,12 @@
       <c r="E18" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>PM112501</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>4, 5, 8</t>
         </is>
@@ -12849,7 +14269,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>ППК25117</t>
         </is>
@@ -12872,12 +14292,12 @@
       <c r="E19" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>OPM1024_01</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>4, 5, 8</t>
         </is>
@@ -12889,7 +14309,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>2156/2025</t>
         </is>
@@ -12912,12 +14332,12 @@
       <c r="E20" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>OPM1024_01</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -12929,7 +14349,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>407/0745/25</t>
         </is>
@@ -12952,12 +14372,12 @@
       <c r="E21" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>OPM1024_01</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -12969,7 +14389,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>ППК25175</t>
         </is>
@@ -12992,12 +14412,12 @@
       <c r="E22" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>GP0824_03</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>4, 5, 8</t>
         </is>
@@ -13009,7 +14429,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>ППК26067</t>
         </is>
@@ -13032,12 +14452,12 @@
       <c r="E23" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>FB012601/1</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>4, 5, 8</t>
         </is>
@@ -13049,7 +14469,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>ППК26069</t>
         </is>
@@ -13072,12 +14492,12 @@
       <c r="E24" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>SCR112501</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>4, 5, 8</t>
         </is>
@@ -13089,7 +14509,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>5887/2025</t>
         </is>
@@ -13112,12 +14532,12 @@
       <c r="E25" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>GP072501/2</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -13129,7 +14549,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>5888/2025</t>
         </is>
@@ -13152,12 +14572,12 @@
       <c r="E26" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>GP082501/1</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -13169,7 +14589,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>4352/2025</t>
         </is>
@@ -13192,12 +14612,12 @@
       <c r="E27" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>HPA052501</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -13209,7 +14629,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>948/1686/25</t>
         </is>
@@ -13232,12 +14652,12 @@
       <c r="E28" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>HPA052501</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -13249,7 +14669,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>10802_2845/2</t>
         </is>
@@ -13272,12 +14692,12 @@
       <c r="E29" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>BSS052501</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -13289,7 +14709,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>ППК25278</t>
         </is>
@@ -13312,12 +14732,12 @@
       <c r="E30" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>HPA052501</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>4, 5, 8</t>
         </is>
@@ -13329,7 +14749,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>10/0013/26</t>
         </is>
@@ -13352,12 +14772,12 @@
       <c r="E31" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>CJ092501</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -13369,7 +14789,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>2/0005/26</t>
         </is>
@@ -13392,12 +14812,12 @@
       <c r="E32" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>OPM092501</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -13409,7 +14829,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>3/0006/26</t>
         </is>
@@ -13432,12 +14852,12 @@
       <c r="E33" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>WC082501</t>
         </is>
       </c>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -13449,7 +14869,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>8/0011/26</t>
         </is>
@@ -13472,12 +14892,12 @@
       <c r="E34" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>CJ082501/1</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -13489,7 +14909,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="19" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>9/0012/26</t>
         </is>
@@ -13512,12 +14932,12 @@
       <c r="E35" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>SJ092501</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -13529,7 +14949,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>5/0008/26</t>
         </is>
@@ -13552,12 +14972,12 @@
       <c r="E36" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F36" s="21" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>GP092501</t>
         </is>
       </c>
-      <c r="G36" s="21" t="inlineStr">
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -13569,7 +14989,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>PP CoA #033</t>
         </is>
@@ -13592,12 +15012,12 @@
       <c r="E37" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>GP092501</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -13609,7 +15029,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>PP CoA #035</t>
         </is>
@@ -13632,12 +15052,12 @@
       <c r="E38" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="21" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>WC082501</t>
         </is>
       </c>
-      <c r="G38" s="21" t="inlineStr">
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>1, 7</t>
         </is>
@@ -13649,7 +15069,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>PP CoA #038</t>
         </is>
@@ -13672,12 +15092,12 @@
       <c r="E39" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F39" s="21" t="inlineStr">
+      <c r="F39" s="22" t="inlineStr">
         <is>
           <t>SJ092501</t>
         </is>
       </c>
-      <c r="G39" s="21" t="inlineStr">
+      <c r="G39" s="22" t="inlineStr">
         <is>
           <t>1, 7</t>
         </is>
@@ -13689,7 +15109,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="19" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>PP CoA #039</t>
         </is>
@@ -13712,12 +15132,12 @@
       <c r="E40" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="21" t="inlineStr">
+      <c r="F40" s="22" t="inlineStr">
         <is>
           <t>CJ092501</t>
         </is>
       </c>
-      <c r="G40" s="21" t="inlineStr">
+      <c r="G40" s="22" t="inlineStr">
         <is>
           <t>1, 7</t>
         </is>
@@ -13729,7 +15149,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="19" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>PP CoA #040</t>
         </is>
@@ -13752,12 +15172,12 @@
       <c r="E41" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F41" s="21" t="inlineStr">
+      <c r="F41" s="22" t="inlineStr">
         <is>
           <t>OPM092501</t>
         </is>
       </c>
-      <c r="G41" s="21" t="inlineStr">
+      <c r="G41" s="22" t="inlineStr">
         <is>
           <t>1, 7</t>
         </is>
@@ -13769,7 +15189,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>PP CoA #041</t>
         </is>
@@ -13792,12 +15212,12 @@
       <c r="E42" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F42" s="21" t="inlineStr">
+      <c r="F42" s="22" t="inlineStr">
         <is>
           <t>CJ082501/1</t>
         </is>
       </c>
-      <c r="G42" s="21" t="inlineStr">
+      <c r="G42" s="22" t="inlineStr">
         <is>
           <t>1, 7</t>
         </is>
@@ -13809,7 +15229,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="19" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>PP CoA #019 / ППК25379</t>
         </is>
@@ -13832,12 +15252,12 @@
       <c r="E43" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F43" s="21" t="inlineStr">
+      <c r="F43" s="22" t="inlineStr">
         <is>
           <t>GP072501/2</t>
         </is>
       </c>
-      <c r="G43" s="21" t="inlineStr">
+      <c r="G43" s="22" t="inlineStr">
         <is>
           <t>4, 5, 8</t>
         </is>
@@ -13849,7 +15269,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="19" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>PP CoA #020 / ППК25380</t>
         </is>
@@ -13872,12 +15292,12 @@
       <c r="E44" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F44" s="21" t="inlineStr">
+      <c r="F44" s="22" t="inlineStr">
         <is>
           <t>GP082501/1</t>
         </is>
       </c>
-      <c r="G44" s="21" t="inlineStr">
+      <c r="G44" s="22" t="inlineStr">
         <is>
           <t>4, 5, 8</t>
         </is>
@@ -13889,7 +15309,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="19" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>PP CoA #027 / ППК25370</t>
         </is>
@@ -13912,12 +15332,12 @@
       <c r="E45" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F45" s="21" t="inlineStr">
+      <c r="F45" s="22" t="inlineStr">
         <is>
           <t>CLE072501</t>
         </is>
       </c>
-      <c r="G45" s="21" t="inlineStr">
+      <c r="G45" s="22" t="inlineStr">
         <is>
           <t>4, 5, 8</t>
         </is>
@@ -13929,7 +15349,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="19" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>ППК26001</t>
         </is>
@@ -13952,12 +15372,12 @@
       <c r="E46" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="F46" s="21" t="inlineStr">
+      <c r="F46" s="22" t="inlineStr">
         <is>
           <t>WC082501</t>
         </is>
       </c>
-      <c r="G46" s="21" t="inlineStr">
+      <c r="G46" s="22" t="inlineStr">
         <is>
           <t>3, 4, 5, 8</t>
         </is>
@@ -13969,7 +15389,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="19" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>ППК26002</t>
         </is>
@@ -13992,12 +15412,12 @@
       <c r="E47" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="F47" s="21" t="inlineStr">
+      <c r="F47" s="22" t="inlineStr">
         <is>
           <t>CJ082501/1</t>
         </is>
       </c>
-      <c r="G47" s="21" t="inlineStr">
+      <c r="G47" s="22" t="inlineStr">
         <is>
           <t>3, 4, 5, 8</t>
         </is>
@@ -14009,7 +15429,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="19" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>ППК26006</t>
         </is>
@@ -14032,12 +15452,12 @@
       <c r="E48" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="F48" s="21" t="inlineStr">
+      <c r="F48" s="22" t="inlineStr">
         <is>
           <t>SJ092501</t>
         </is>
       </c>
-      <c r="G48" s="21" t="inlineStr">
+      <c r="G48" s="22" t="inlineStr">
         <is>
           <t>3, 4, 5, 8</t>
         </is>
@@ -14049,7 +15469,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="19" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>ППК26007</t>
         </is>
@@ -14072,12 +15492,12 @@
       <c r="E49" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="F49" s="21" t="inlineStr">
+      <c r="F49" s="22" t="inlineStr">
         <is>
           <t>CJ092501</t>
         </is>
       </c>
-      <c r="G49" s="21" t="inlineStr">
+      <c r="G49" s="22" t="inlineStr">
         <is>
           <t>3, 4, 5, 8</t>
         </is>
@@ -14089,7 +15509,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="19" t="inlineStr">
+      <c r="A50" s="21" t="inlineStr">
         <is>
           <t>ППК26008</t>
         </is>
@@ -14112,12 +15532,12 @@
       <c r="E50" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="F50" s="21" t="inlineStr">
+      <c r="F50" s="22" t="inlineStr">
         <is>
           <t>OPM092501</t>
         </is>
       </c>
-      <c r="G50" s="21" t="inlineStr">
+      <c r="G50" s="22" t="inlineStr">
         <is>
           <t>3, 4, 5, 8</t>
         </is>
@@ -14129,7 +15549,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="19" t="inlineStr">
+      <c r="A51" s="21" t="inlineStr">
         <is>
           <t>ППК26009</t>
         </is>
@@ -14152,12 +15572,12 @@
       <c r="E51" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="F51" s="21" t="inlineStr">
+      <c r="F51" s="22" t="inlineStr">
         <is>
           <t>GP092501</t>
         </is>
       </c>
-      <c r="G51" s="21" t="inlineStr">
+      <c r="G51" s="22" t="inlineStr">
         <is>
           <t>3, 4, 5, 8</t>
         </is>
@@ -14169,7 +15589,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="19" t="inlineStr">
+      <c r="A52" s="21" t="inlineStr">
         <is>
           <t>n/a — Purely Plant in-house CoA (Batch GG1024, no certificate/report number printed)</t>
         </is>
@@ -14192,12 +15612,12 @@
       <c r="E52" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F52" s="21" t="inlineStr">
+      <c r="F52" s="22" t="inlineStr">
         <is>
           <t>GG1024</t>
         </is>
       </c>
-      <c r="G52" s="21" t="inlineStr">
+      <c r="G52" s="22" t="inlineStr">
         <is>
           <t>1, 7</t>
         </is>
@@ -14209,7 +15629,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="19" t="inlineStr">
+      <c r="A53" s="21" t="inlineStr">
         <is>
           <t>n/a — Purely Plant in-house CoA (Batch GG1024, no certificate/report number printed)</t>
         </is>
@@ -14232,12 +15652,12 @@
       <c r="E53" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="F53" s="21" t="inlineStr">
+      <c r="F53" s="22" t="inlineStr">
         <is>
           <t>GG1024</t>
         </is>
       </c>
-      <c r="G53" s="21" t="inlineStr">
+      <c r="G53" s="22" t="inlineStr">
         <is>
           <t>3, 4, 5, 9.1, 9.2, 9.3, 9.4, 9.5, 10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -14249,7 +15669,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="19" t="inlineStr">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>ППК25321</t>
         </is>
@@ -14272,12 +15692,12 @@
       <c r="E54" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="F54" s="21" t="inlineStr">
+      <c r="F54" s="22" t="inlineStr">
         <is>
           <t>CJ062501/1</t>
         </is>
       </c>
-      <c r="G54" s="21" t="inlineStr">
+      <c r="G54" s="22" t="inlineStr">
         <is>
           <t>3, 4, 5, 8</t>
         </is>
@@ -14289,7 +15709,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="19" t="inlineStr">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>4907/2025</t>
         </is>
@@ -14312,12 +15732,12 @@
       <c r="E55" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F55" s="21" t="inlineStr">
+      <c r="F55" s="22" t="inlineStr">
         <is>
           <t>CJ062501/1</t>
         </is>
       </c>
-      <c r="G55" s="21" t="inlineStr">
+      <c r="G55" s="22" t="inlineStr">
         <is>
           <t>10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -14329,7 +15749,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="19" t="inlineStr">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>1157/2058/25</t>
         </is>
@@ -14352,12 +15772,12 @@
       <c r="E56" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F56" s="21" t="inlineStr">
+      <c r="F56" s="22" t="inlineStr">
         <is>
           <t>BSS052501</t>
         </is>
       </c>
-      <c r="G56" s="21" t="inlineStr">
+      <c r="G56" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -14369,7 +15789,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="19" t="inlineStr">
+      <c r="A57" s="21" t="inlineStr">
         <is>
           <t>3178/2025</t>
         </is>
@@ -14392,12 +15812,12 @@
       <c r="E57" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F57" s="21" t="inlineStr">
+      <c r="F57" s="22" t="inlineStr">
         <is>
           <t>GP0824_03</t>
         </is>
       </c>
-      <c r="G57" s="21" t="inlineStr">
+      <c r="G57" s="22" t="inlineStr">
         <is>
           <t>10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -14409,7 +15829,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="19" t="inlineStr">
+      <c r="A58" s="21" t="inlineStr">
         <is>
           <t>1219/2170/25</t>
         </is>
@@ -14432,12 +15852,12 @@
       <c r="E58" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F58" s="21" t="inlineStr">
+      <c r="F58" s="22" t="inlineStr">
         <is>
           <t>CLE072501</t>
         </is>
       </c>
-      <c r="G58" s="21" t="inlineStr">
+      <c r="G58" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -14449,7 +15869,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="19" t="inlineStr">
+      <c r="A59" s="21" t="inlineStr">
         <is>
           <t>3636/2025</t>
         </is>
@@ -14472,12 +15892,12 @@
       <c r="E59" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F59" s="21" t="inlineStr">
+      <c r="F59" s="22" t="inlineStr">
         <is>
           <t>OPM1024_03</t>
         </is>
       </c>
-      <c r="G59" s="21" t="inlineStr">
+      <c r="G59" s="22" t="inlineStr">
         <is>
           <t>10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -14489,7 +15909,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="19" t="inlineStr">
+      <c r="A60" s="21" t="inlineStr">
         <is>
           <t>3638/2025</t>
         </is>
@@ -14512,12 +15932,12 @@
       <c r="E60" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F60" s="21" t="inlineStr">
+      <c r="F60" s="22" t="inlineStr">
         <is>
           <t>MB0824_05</t>
         </is>
       </c>
-      <c r="G60" s="21" t="inlineStr">
+      <c r="G60" s="22" t="inlineStr">
         <is>
           <t>10.2, 11.1, 11.2, 11.3, 11.4, 12</t>
         </is>
@@ -14529,7 +15949,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="19" t="inlineStr">
+      <c r="A61" s="21" t="inlineStr">
         <is>
           <t>ППК25210</t>
         </is>
@@ -14552,12 +15972,12 @@
       <c r="E61" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F61" s="21" t="inlineStr">
+      <c r="F61" s="22" t="inlineStr">
         <is>
           <t>OPM1024_03</t>
         </is>
       </c>
-      <c r="G61" s="21" t="inlineStr">
+      <c r="G61" s="22" t="inlineStr">
         <is>
           <t>4, 5, 8</t>
         </is>
@@ -14569,7 +15989,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="19" t="inlineStr">
+      <c r="A62" s="21" t="inlineStr">
         <is>
           <t>ППК52211</t>
         </is>
@@ -14592,12 +16012,12 @@
       <c r="E62" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F62" s="21" t="inlineStr">
+      <c r="F62" s="22" t="inlineStr">
         <is>
           <t>MB0824_05</t>
         </is>
       </c>
-      <c r="G62" s="21" t="inlineStr">
+      <c r="G62" s="22" t="inlineStr">
         <is>
           <t>4, 5, 8</t>
         </is>
@@ -14609,7 +16029,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="19" t="inlineStr">
+      <c r="A63" s="21" t="inlineStr">
         <is>
           <t>In-house GC cross-check NGP/QCG/SOP-024</t>
         </is>
@@ -14632,12 +16052,12 @@
       <c r="E63" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="F63" s="21" t="inlineStr">
+      <c r="F63" s="22" t="inlineStr">
         <is>
           <t>BSS052501</t>
         </is>
       </c>
-      <c r="G63" s="21" t="inlineStr">
+      <c r="G63" s="22" t="inlineStr">
         <is>
           <t>3, 4, 5, 8</t>
         </is>
@@ -14649,7 +16069,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="19" t="inlineStr">
+      <c r="A64" s="21" t="inlineStr">
         <is>
           <t>766/1375/25</t>
         </is>
@@ -14672,12 +16092,12 @@
       <c r="E64" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F64" s="21" t="inlineStr">
+      <c r="F64" s="22" t="inlineStr">
         <is>
           <t>OPM1024_03</t>
         </is>
       </c>
-      <c r="G64" s="21" t="inlineStr">
+      <c r="G64" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -14689,7 +16109,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="19" t="inlineStr">
+      <c r="A65" s="21" t="inlineStr">
         <is>
           <t>767/1376/25</t>
         </is>
@@ -14712,12 +16132,12 @@
       <c r="E65" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F65" s="21" t="inlineStr">
+      <c r="F65" s="22" t="inlineStr">
         <is>
           <t>MB0824_05</t>
         </is>
       </c>
-      <c r="G65" s="21" t="inlineStr">
+      <c r="G65" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -14729,7 +16149,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="19" t="inlineStr">
+      <c r="A66" s="21" t="inlineStr">
         <is>
           <t>ППК26111</t>
         </is>
@@ -14752,12 +16172,12 @@
       <c r="E66" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F66" s="21" t="inlineStr">
+      <c r="F66" s="22" t="inlineStr">
         <is>
           <t>JD012603/2V</t>
         </is>
       </c>
-      <c r="G66" s="21" t="inlineStr">
+      <c r="G66" s="22" t="inlineStr">
         <is>
           <t>3, 4, 5, 6, 7, 8</t>
         </is>
@@ -14769,7 +16189,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="19" t="inlineStr">
+      <c r="A67" s="21" t="inlineStr">
         <is>
           <t>ППК26113</t>
         </is>
@@ -14792,12 +16212,12 @@
       <c r="E67" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F67" s="21" t="inlineStr">
+      <c r="F67" s="22" t="inlineStr">
         <is>
           <t>JD012603/2</t>
         </is>
       </c>
-      <c r="G67" s="21" t="inlineStr">
+      <c r="G67" s="22" t="inlineStr">
         <is>
           <t>3, 4, 5, 6, 7, 8</t>
         </is>
@@ -14809,7 +16229,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="19" t="inlineStr">
+      <c r="A68" s="21" t="inlineStr">
         <is>
           <t>1226/2192/25</t>
         </is>
@@ -14832,12 +16252,12 @@
       <c r="E68" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F68" s="21" t="inlineStr">
+      <c r="F68" s="22" t="inlineStr">
         <is>
           <t>GP082501/1</t>
         </is>
       </c>
-      <c r="G68" s="21" t="inlineStr">
+      <c r="G68" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -14849,7 +16269,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="19" t="inlineStr">
+      <c r="A69" s="21" t="inlineStr">
         <is>
           <t>1229/2195/25</t>
         </is>
@@ -14872,12 +16292,12 @@
       <c r="E69" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F69" s="21" t="inlineStr">
+      <c r="F69" s="22" t="inlineStr">
         <is>
           <t>GP072501/2</t>
         </is>
       </c>
-      <c r="G69" s="21" t="inlineStr">
+      <c r="G69" s="22" t="inlineStr">
         <is>
           <t>9.1, 9.2, 9.3, 9.4, 9.5</t>
         </is>
@@ -14889,7 +16309,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="19" t="inlineStr">
+      <c r="A70" s="21" t="inlineStr">
         <is>
           <t>PP CoA #033</t>
         </is>
@@ -14912,12 +16332,12 @@
       <c r="E70" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F70" s="21" t="inlineStr">
+      <c r="F70" s="22" t="inlineStr">
         <is>
           <t>GP092501</t>
         </is>
       </c>
-      <c r="G70" s="21" t="inlineStr">
+      <c r="G70" s="22" t="inlineStr">
         <is>
           <t>7</t>
         </is>
